--- a/Vibration_Matlab/弹簧参数组合.xlsx
+++ b/Vibration_Matlab/弹簧参数组合.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="60" uniqueCount="20">
   <si>
     <t>k1</t>
   </si>
@@ -1510,7 +1510,7 @@
     </row>
     <row r="2">
       <c r="A2" s="5">
-        <v>2644</v>
+        <v>2791</v>
       </c>
       <c r="B2" s="6">
         <v>97.701637350966649</v>
@@ -1525,10 +1525,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F2" s="6">
-        <v>2806.7940552016985</v>
+        <v>2962.8450106157115</v>
       </c>
       <c r="G2" s="6">
-        <v>1406.2038216560509</v>
+        <v>1484.3853503184714</v>
       </c>
       <c r="H2" s="6">
         <v>60</v>
@@ -1543,7 +1543,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L2" s="6">
-        <v>9.8338273187131566</v>
+        <v>9.8338273187131584</v>
       </c>
       <c r="M2" s="6">
         <v>119.20529801324503</v>
@@ -1555,24 +1555,24 @@
         <v>12</v>
       </c>
       <c r="P2" s="6">
-        <v>3.1046304353754799</v>
+        <v>2.7380266815885688</v>
       </c>
       <c r="Q2" s="6">
-        <v>37.255565224505759</v>
+        <v>32.856320179062827</v>
       </c>
       <c r="R2" s="6">
-        <v>6.5404173190191699</v>
+        <v>7.4513234080464423</v>
       </c>
       <c r="S2" s="6">
-        <v>6.1610731145160589</v>
+        <v>7.0191466503797484</v>
       </c>
       <c r="T2" s="7">
-        <v>12.297551126778561</v>
+        <v>14.010272755249</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5">
-        <v>2645</v>
+        <v>2792</v>
       </c>
       <c r="B3" s="6">
         <v>97.701637350966649</v>
@@ -1587,10 +1587,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F3" s="6">
-        <v>2807.8556263269643</v>
+        <v>2963.9065817409769</v>
       </c>
       <c r="G3" s="6">
-        <v>1406.7356687898091</v>
+        <v>1484.9171974522294</v>
       </c>
       <c r="H3" s="6">
         <v>60</v>
@@ -1605,36 +1605,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L3" s="6">
-        <v>9.8338273187131424</v>
+        <v>9.8338273187131477</v>
       </c>
       <c r="M3" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N3" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O3" s="6">
         <v>12</v>
       </c>
       <c r="P3" s="6">
-        <v>3.1046304353754799</v>
+        <v>2.7380266815885688</v>
       </c>
       <c r="Q3" s="6">
-        <v>37.255565224505759</v>
+        <v>32.856320179062827</v>
       </c>
       <c r="R3" s="6">
-        <v>6.5379445714505433</v>
+        <v>7.4486545959375441</v>
       </c>
       <c r="S3" s="6">
-        <v>6.1587437863064105</v>
+        <v>7.0166326293731647</v>
       </c>
       <c r="T3" s="7">
-        <v>12.292901769074671</v>
+        <v>14.005254749247834</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5">
-        <v>2646</v>
+        <v>2793</v>
       </c>
       <c r="B4" s="6">
         <v>97.701637350966649</v>
@@ -1649,10 +1649,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F4" s="6">
-        <v>2808.9171974522296</v>
+        <v>2964.9681528662422</v>
       </c>
       <c r="G4" s="6">
-        <v>1407.2675159235671</v>
+        <v>1485.4490445859874</v>
       </c>
       <c r="H4" s="6">
         <v>60</v>
@@ -1667,7 +1667,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L4" s="6">
-        <v>9.8338273187131406</v>
+        <v>9.833827318713146</v>
       </c>
       <c r="M4" s="6">
         <v>119.20529801324503</v>
@@ -1679,24 +1679,24 @@
         <v>12</v>
       </c>
       <c r="P4" s="6">
-        <v>3.1046304353754799</v>
+        <v>2.7380266815885688</v>
       </c>
       <c r="Q4" s="6">
-        <v>37.255565224505759</v>
+        <v>32.856320179062827</v>
       </c>
       <c r="R4" s="6">
-        <v>6.535473692927698</v>
+        <v>7.4459876949006878</v>
       </c>
       <c r="S4" s="6">
-        <v>6.1564162187378901</v>
+        <v>7.0141204085964475</v>
       </c>
       <c r="T4" s="7">
-        <v>12.288255925624531</v>
+        <v>14.000240336519855</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5">
-        <v>2647</v>
+        <v>2794</v>
       </c>
       <c r="B5" s="6">
         <v>97.701637350966649</v>
@@ -1711,10 +1711,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F5" s="6">
-        <v>2809.978768577495</v>
+        <v>2966.0297239915076</v>
       </c>
       <c r="G5" s="6">
-        <v>1407.7993630573251</v>
+        <v>1485.9808917197454</v>
       </c>
       <c r="H5" s="6">
         <v>60</v>
@@ -1729,36 +1729,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L5" s="6">
-        <v>9.8338273187131495</v>
+        <v>9.8338273187131442</v>
       </c>
       <c r="M5" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N5" s="6">
-        <v>153.1265226962625</v>
+        <v>153.12652269626247</v>
       </c>
       <c r="O5" s="6">
         <v>12</v>
       </c>
       <c r="P5" s="6">
-        <v>3.1046304353754799</v>
+        <v>2.7380266815885688</v>
       </c>
       <c r="Q5" s="6">
-        <v>37.255565224505759</v>
+        <v>32.856320179062827</v>
       </c>
       <c r="R5" s="6">
-        <v>6.5330046813323346</v>
+        <v>7.4433227028839015</v>
       </c>
       <c r="S5" s="6">
-        <v>6.1540904098150575</v>
+        <v>7.0116099861166354</v>
       </c>
       <c r="T5" s="7">
-        <v>12.283613592445224</v>
+        <v>13.995229513206853</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5">
-        <v>2648</v>
+        <v>2795</v>
       </c>
       <c r="B6" s="6">
         <v>97.701637350966649</v>
@@ -1773,10 +1773,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F6" s="6">
-        <v>2811.0403397027603</v>
+        <v>2967.0912951167729</v>
       </c>
       <c r="G6" s="6">
-        <v>1408.3312101910828</v>
+        <v>1486.5127388535032</v>
       </c>
       <c r="H6" s="6">
         <v>60</v>
@@ -1791,7 +1791,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L6" s="6">
-        <v>9.8338273187131477</v>
+        <v>9.8338273187131531</v>
       </c>
       <c r="M6" s="6">
         <v>119.20529801324503</v>
@@ -1803,24 +1803,24 @@
         <v>12</v>
       </c>
       <c r="P6" s="6">
-        <v>3.1046304353754799</v>
+        <v>2.7380266815885688</v>
       </c>
       <c r="Q6" s="6">
-        <v>37.255565224505759</v>
+        <v>32.856320179062827</v>
       </c>
       <c r="R6" s="6">
-        <v>6.530537534549353</v>
+        <v>7.4406596178381479</v>
       </c>
       <c r="S6" s="6">
-        <v>6.1517663575454904</v>
+        <v>7.0091013600035348</v>
       </c>
       <c r="T6" s="7">
-        <v>12.278974765559862</v>
+        <v>13.990222275456157</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5">
-        <v>2649</v>
+        <v>2796</v>
       </c>
       <c r="B7" s="6">
         <v>97.701637350966649</v>
@@ -1835,10 +1835,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F7" s="6">
-        <v>2812.1019108280257</v>
+        <v>2968.1528662420383</v>
       </c>
       <c r="G7" s="6">
-        <v>1408.8630573248408</v>
+        <v>1487.0445859872611</v>
       </c>
       <c r="H7" s="6">
         <v>60</v>
@@ -1853,7 +1853,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L7" s="6">
-        <v>9.8338273187131673</v>
+        <v>9.8338273187131513</v>
       </c>
       <c r="M7" s="6">
         <v>119.20529801324503</v>
@@ -1865,24 +1865,24 @@
         <v>12</v>
       </c>
       <c r="P7" s="6">
-        <v>3.1046304353754799</v>
+        <v>2.7380266815885688</v>
       </c>
       <c r="Q7" s="6">
-        <v>37.255565224505759</v>
+        <v>32.856320179062827</v>
       </c>
       <c r="R7" s="6">
-        <v>6.5280722504668507</v>
+        <v>7.4379984377173178</v>
       </c>
       <c r="S7" s="6">
-        <v>6.1494440599397731</v>
+        <v>7.0065945283297131</v>
       </c>
       <c r="T7" s="7">
-        <v>12.274339440997551</v>
+        <v>13.985218619420586</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5">
-        <v>2650</v>
+        <v>2797</v>
       </c>
       <c r="B8" s="6">
         <v>97.701637350966649</v>
@@ -1897,10 +1897,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F8" s="6">
-        <v>2813.163481953291</v>
+        <v>2969.2144373673036</v>
       </c>
       <c r="G8" s="6">
-        <v>1409.3949044585988</v>
+        <v>1487.5764331210191</v>
       </c>
       <c r="H8" s="6">
         <v>60</v>
@@ -1915,36 +1915,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L8" s="6">
-        <v>9.8338273187131442</v>
+        <v>9.8338273187131495</v>
       </c>
       <c r="M8" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N8" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O8" s="6">
         <v>12</v>
       </c>
       <c r="P8" s="6">
-        <v>3.1046304353754799</v>
+        <v>2.7380266815885688</v>
       </c>
       <c r="Q8" s="6">
-        <v>37.255565224505759</v>
+        <v>32.856320179062827</v>
       </c>
       <c r="R8" s="6">
-        <v>6.5256088269761081</v>
+        <v>7.4353391604782333</v>
       </c>
       <c r="S8" s="6">
-        <v>6.1471235150114936</v>
+        <v>7.0040894891704966</v>
       </c>
       <c r="T8" s="7">
-        <v>12.269707614793399</v>
+        <v>13.980218541258477</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5">
-        <v>2651</v>
+        <v>2798</v>
       </c>
       <c r="B9" s="6">
         <v>97.701637350966649</v>
@@ -1959,10 +1959,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F9" s="6">
-        <v>2814.2250530785564</v>
+        <v>2970.276008492569</v>
       </c>
       <c r="G9" s="6">
-        <v>1409.9267515923568</v>
+        <v>1488.1082802547771</v>
       </c>
       <c r="H9" s="6">
         <v>60</v>
@@ -1977,7 +1977,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L9" s="6">
-        <v>9.8338273187131531</v>
+        <v>9.8338273187131566</v>
       </c>
       <c r="M9" s="6">
         <v>119.20529801324503</v>
@@ -1989,24 +1989,24 @@
         <v>12</v>
       </c>
       <c r="P9" s="6">
-        <v>3.1046304353754799</v>
+        <v>2.7380266815885688</v>
       </c>
       <c r="Q9" s="6">
-        <v>37.255565224505759</v>
+        <v>32.856320179062827</v>
       </c>
       <c r="R9" s="6">
-        <v>6.5231472619715909</v>
+        <v>7.4326817840806365</v>
       </c>
       <c r="S9" s="6">
-        <v>6.1448047207772394</v>
+        <v>7.0015862406039595</v>
       </c>
       <c r="T9" s="7">
-        <v>12.2650792829885</v>
+        <v>13.975222037133651</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5">
-        <v>2652</v>
+        <v>2799</v>
       </c>
       <c r="B10" s="6">
         <v>97.701637350966649</v>
@@ -2021,10 +2021,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F10" s="6">
-        <v>2815.2866242038217</v>
+        <v>2971.3375796178348</v>
       </c>
       <c r="G10" s="6">
-        <v>1410.4585987261146</v>
+        <v>1488.6401273885351</v>
       </c>
       <c r="H10" s="6">
         <v>60</v>
@@ -2039,36 +2039,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L10" s="6">
-        <v>9.8338273187131406</v>
+        <v>9.8338273187131549</v>
       </c>
       <c r="M10" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N10" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O10" s="6">
         <v>12</v>
       </c>
       <c r="P10" s="6">
-        <v>3.1046304353754799</v>
+        <v>2.7380266815885688</v>
       </c>
       <c r="Q10" s="6">
-        <v>37.255565224505759</v>
+        <v>32.856320179062827</v>
       </c>
       <c r="R10" s="6">
-        <v>6.5206875533509372</v>
+        <v>7.4300263064871821</v>
       </c>
       <c r="S10" s="6">
-        <v>6.1424876752565831</v>
+        <v>6.9990847807109242</v>
       </c>
       <c r="T10" s="7">
-        <v>12.260454441629907</v>
+        <v>13.97022910321542</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5">
-        <v>2653</v>
+        <v>2800</v>
       </c>
       <c r="B11" s="6">
         <v>97.701637350966649</v>
@@ -2083,10 +2083,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F11" s="6">
-        <v>2816.348195329087</v>
+        <v>2972.3991507431001</v>
       </c>
       <c r="G11" s="6">
-        <v>1410.9904458598726</v>
+        <v>1489.1719745222931</v>
       </c>
       <c r="H11" s="6">
         <v>60</v>
@@ -2101,36 +2101,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L11" s="6">
-        <v>9.8338273187131406</v>
+        <v>9.8338273187131531</v>
       </c>
       <c r="M11" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N11" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O11" s="6">
         <v>12</v>
       </c>
       <c r="P11" s="6">
-        <v>3.1046304353754799</v>
+        <v>2.7380266815885688</v>
       </c>
       <c r="Q11" s="6">
-        <v>37.255565224505759</v>
+        <v>32.856320179062827</v>
       </c>
       <c r="R11" s="6">
-        <v>6.5182296990149595</v>
+        <v>7.427372725663437</v>
       </c>
       <c r="S11" s="6">
-        <v>6.1401723764720915</v>
+        <v>6.9965851075749566</v>
       </c>
       <c r="T11" s="7">
-        <v>12.255833086770643</v>
+        <v>13.965239735678557</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5">
-        <v>2654</v>
+        <v>2801</v>
       </c>
       <c r="B12" s="6">
         <v>97.701637350966649</v>
@@ -2145,10 +2145,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F12" s="6">
-        <v>2817.4097664543524</v>
+        <v>2973.4607218683655</v>
       </c>
       <c r="G12" s="6">
-        <v>1411.5222929936306</v>
+        <v>1489.7038216560511</v>
       </c>
       <c r="H12" s="6">
         <v>60</v>
@@ -2163,7 +2163,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L12" s="6">
-        <v>9.8338273187131477</v>
+        <v>9.8338273187131513</v>
       </c>
       <c r="M12" s="6">
         <v>119.20529801324503</v>
@@ -2175,24 +2175,24 @@
         <v>12</v>
       </c>
       <c r="P12" s="6">
-        <v>3.1046304353754799</v>
+        <v>2.7380266815885688</v>
       </c>
       <c r="Q12" s="6">
-        <v>37.255565224505759</v>
+        <v>32.856320179062827</v>
       </c>
       <c r="R12" s="6">
-        <v>6.5157736968676296</v>
+        <v>7.4247210395778724</v>
       </c>
       <c r="S12" s="6">
-        <v>6.1378588224493065</v>
+        <v>6.9940872192823553</v>
       </c>
       <c r="T12" s="7">
-        <v>12.251215214469674</v>
+        <v>13.960253930703303</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5">
-        <v>2655</v>
+        <v>2802</v>
       </c>
       <c r="B13" s="6">
         <v>97.701637350966649</v>
@@ -2207,10 +2207,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F13" s="6">
-        <v>2818.4713375796182</v>
+        <v>2974.5222929936308</v>
       </c>
       <c r="G13" s="6">
-        <v>1412.0541401273888</v>
+        <v>1490.2356687898091</v>
       </c>
       <c r="H13" s="6">
         <v>60</v>
@@ -2225,7 +2225,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L13" s="6">
-        <v>9.833827318713146</v>
+        <v>9.8338273187131389</v>
       </c>
       <c r="M13" s="6">
         <v>119.20529801324503</v>
@@ -2237,24 +2237,24 @@
         <v>12</v>
       </c>
       <c r="P13" s="6">
-        <v>3.1046304353754799</v>
+        <v>2.7380266815885688</v>
       </c>
       <c r="Q13" s="6">
-        <v>37.255565224505759</v>
+        <v>32.856320179062827</v>
       </c>
       <c r="R13" s="6">
-        <v>6.5133195448160786</v>
+        <v>7.4220712462018623</v>
       </c>
       <c r="S13" s="6">
-        <v>6.1355470112167447</v>
+        <v>6.9915911139221549</v>
       </c>
       <c r="T13" s="7">
-        <v>12.246600820791906</v>
+        <v>13.955271684475358</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5">
-        <v>2656</v>
+        <v>2803</v>
       </c>
       <c r="B14" s="6">
         <v>97.701637350966649</v>
@@ -2269,10 +2269,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F14" s="6">
-        <v>2819.5329087048835</v>
+        <v>2975.5838641188961</v>
       </c>
       <c r="G14" s="6">
-        <v>1412.5859872611466</v>
+        <v>1490.7675159235669</v>
       </c>
       <c r="H14" s="6">
         <v>60</v>
@@ -2287,7 +2287,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L14" s="6">
-        <v>9.8338273187131637</v>
+        <v>9.8338273187131477</v>
       </c>
       <c r="M14" s="6">
         <v>119.20529801324503</v>
@@ -2299,24 +2299,24 @@
         <v>12</v>
       </c>
       <c r="P14" s="6">
-        <v>3.1046304353754799</v>
+        <v>2.7380266815885688</v>
       </c>
       <c r="Q14" s="6">
-        <v>37.255565224505759</v>
+        <v>32.856320179062827</v>
       </c>
       <c r="R14" s="6">
-        <v>6.5108672407705894</v>
+        <v>7.4194233435096759</v>
       </c>
       <c r="S14" s="6">
-        <v>6.1332369408058955</v>
+        <v>6.9890967895861138</v>
       </c>
       <c r="T14" s="7">
-        <v>12.241989901808173</v>
+        <v>13.950292993185856</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5">
-        <v>2910</v>
+        <v>2804</v>
       </c>
       <c r="B15" s="6">
         <v>97.701637350966649</v>
@@ -2331,10 +2331,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F15" s="6">
-        <v>3089.1719745222931</v>
+        <v>2976.6454352441615</v>
       </c>
       <c r="G15" s="6">
-        <v>1547.6751592356688</v>
+        <v>1491.2993630573249</v>
       </c>
       <c r="H15" s="6">
         <v>60</v>
@@ -2349,7 +2349,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L15" s="6">
-        <v>9.8338273187131442</v>
+        <v>9.833827318713146</v>
       </c>
       <c r="M15" s="6">
         <v>119.20529801324503</v>
@@ -2358,27 +2358,27 @@
         <v>153.12652269626247</v>
       </c>
       <c r="O15" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P15" s="6">
-        <v>2.9876564346371177</v>
+        <v>2.7380266815885688</v>
       </c>
       <c r="Q15" s="6">
-        <v>32.864220781008292</v>
+        <v>32.856320179062827</v>
       </c>
       <c r="R15" s="6">
-        <v>7.4243826653814926</v>
+        <v>7.4167773294784674</v>
       </c>
       <c r="S15" s="6">
-        <v>6.9937684707893668</v>
+        <v>6.9866042443687153</v>
       </c>
       <c r="T15" s="7">
-        <v>13.9596177061664</v>
+        <v>13.945317853031369</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5">
-        <v>2911</v>
+        <v>2805</v>
       </c>
       <c r="B16" s="6">
         <v>97.701637350966649</v>
@@ -2393,10 +2393,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F16" s="6">
-        <v>3090.2335456475585</v>
+        <v>2977.7070063694268</v>
       </c>
       <c r="G16" s="6">
-        <v>1548.2070063694268</v>
+        <v>1491.8312101910828</v>
       </c>
       <c r="H16" s="6">
         <v>60</v>
@@ -2411,7 +2411,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L16" s="6">
-        <v>9.8338273187131513</v>
+        <v>9.8338273187131637</v>
       </c>
       <c r="M16" s="6">
         <v>119.20529801324503</v>
@@ -2420,27 +2420,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O16" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P16" s="6">
-        <v>2.9876564346371177</v>
+        <v>2.7380266815885688</v>
       </c>
       <c r="Q16" s="6">
-        <v>32.864220781008292</v>
+        <v>32.856320179062827</v>
       </c>
       <c r="R16" s="6">
-        <v>7.4218322075782019</v>
+        <v>7.4141332020882782</v>
       </c>
       <c r="S16" s="6">
-        <v>6.9913659395386665</v>
+        <v>6.984113476367158</v>
       </c>
       <c r="T16" s="7">
-        <v>13.954822234608114</v>
+        <v>13.940346260213889</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5">
-        <v>2912</v>
+        <v>2806</v>
       </c>
       <c r="B17" s="6">
         <v>97.701637350966649</v>
@@ -2455,10 +2455,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F17" s="6">
-        <v>3091.2951167728238</v>
+        <v>2978.7685774946922</v>
       </c>
       <c r="G17" s="6">
-        <v>1548.7388535031848</v>
+        <v>1492.3630573248408</v>
       </c>
       <c r="H17" s="6">
         <v>60</v>
@@ -2473,7 +2473,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L17" s="6">
-        <v>9.8338273187131406</v>
+        <v>9.8338273187131424</v>
       </c>
       <c r="M17" s="6">
         <v>119.20529801324503</v>
@@ -2482,27 +2482,27 @@
         <v>153.12652269626247</v>
       </c>
       <c r="O17" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P17" s="6">
-        <v>2.9876564346371177</v>
+        <v>2.7380266815885688</v>
       </c>
       <c r="Q17" s="6">
-        <v>32.864220781008292</v>
+        <v>32.856320179062827</v>
       </c>
       <c r="R17" s="6">
-        <v>7.4192835014629628</v>
+        <v>7.4114909593220313</v>
       </c>
       <c r="S17" s="6">
-        <v>6.9889650583781098</v>
+        <v>6.9816244836813537</v>
       </c>
       <c r="T17" s="7">
-        <v>13.950030056642934</v>
+        <v>13.935378210940826</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5">
-        <v>2913</v>
+        <v>2807</v>
       </c>
       <c r="B18" s="6">
         <v>97.701637350966649</v>
@@ -2517,10 +2517,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F18" s="6">
-        <v>3092.3566878980891</v>
+        <v>2979.8301486199575</v>
       </c>
       <c r="G18" s="6">
-        <v>1549.2707006369426</v>
+        <v>1492.8949044585988</v>
       </c>
       <c r="H18" s="6">
         <v>60</v>
@@ -2535,7 +2535,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L18" s="6">
-        <v>9.8338273187131495</v>
+        <v>9.8338273187131513</v>
       </c>
       <c r="M18" s="6">
         <v>119.20529801324503</v>
@@ -2544,27 +2544,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O18" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P18" s="6">
-        <v>2.9876564346371177</v>
+        <v>2.7380266815885688</v>
       </c>
       <c r="Q18" s="6">
-        <v>32.864220781008292</v>
+        <v>32.856320179062827</v>
       </c>
       <c r="R18" s="6">
-        <v>7.4167365452317702</v>
+        <v>7.4088505991655227</v>
       </c>
       <c r="S18" s="6">
-        <v>6.9865658256083272</v>
+        <v>6.9791372644139225</v>
       </c>
       <c r="T18" s="7">
-        <v>13.945241168878896</v>
+        <v>13.930413701424992</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5">
-        <v>2914</v>
+        <v>3072</v>
       </c>
       <c r="B19" s="6">
         <v>97.701637350966649</v>
@@ -2579,10 +2579,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F19" s="6">
-        <v>3093.4182590233549</v>
+        <v>3261.1464968152868</v>
       </c>
       <c r="G19" s="6">
-        <v>1549.8025477707008</v>
+        <v>1633.8343949044588</v>
       </c>
       <c r="H19" s="6">
         <v>60</v>
@@ -2597,7 +2597,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L19" s="6">
-        <v>9.8338273187131549</v>
+        <v>9.8338273187131495</v>
       </c>
       <c r="M19" s="6">
         <v>119.20529801324503</v>
@@ -2609,24 +2609,24 @@
         <v>11</v>
       </c>
       <c r="P19" s="6">
-        <v>2.9876564346371177</v>
+        <v>2.6348653096505714</v>
       </c>
       <c r="Q19" s="6">
-        <v>32.864220781008292</v>
+        <v>28.983518406156286</v>
       </c>
       <c r="R19" s="6">
-        <v>7.4141913370830963</v>
+        <v>8.4578205192005314</v>
       </c>
       <c r="S19" s="6">
-        <v>6.9841682395322762</v>
+        <v>7.9672669290869012</v>
       </c>
       <c r="T19" s="7">
-        <v>13.940455567928696</v>
+        <v>15.902728401371061</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5">
-        <v>2915</v>
+        <v>3073</v>
       </c>
       <c r="B20" s="6">
         <v>97.701637350966649</v>
@@ -2641,10 +2641,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F20" s="6">
-        <v>3094.4798301486203</v>
+        <v>3262.2080679405522</v>
       </c>
       <c r="G20" s="6">
-        <v>1550.3343949044588</v>
+        <v>1634.3662420382166</v>
       </c>
       <c r="H20" s="6">
         <v>60</v>
@@ -2659,7 +2659,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L20" s="6">
-        <v>9.8338273187131531</v>
+        <v>9.8338273187131566</v>
       </c>
       <c r="M20" s="6">
         <v>119.20529801324503</v>
@@ -2671,24 +2671,24 @@
         <v>11</v>
       </c>
       <c r="P20" s="6">
-        <v>2.9876564346371177</v>
+        <v>2.6348653096505714</v>
       </c>
       <c r="Q20" s="6">
-        <v>32.864220781008292</v>
+        <v>28.983518406156286</v>
       </c>
       <c r="R20" s="6">
-        <v>7.4116478752178887</v>
+        <v>8.455068218348206</v>
       </c>
       <c r="S20" s="6">
-        <v>6.9817722984552502</v>
+        <v>7.9646742616840092</v>
       </c>
       <c r="T20" s="7">
-        <v>13.935673250409682</v>
+        <v>15.897553416534949</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5">
-        <v>2916</v>
+        <v>3074</v>
       </c>
       <c r="B21" s="6">
         <v>97.701637350966649</v>
@@ -2703,10 +2703,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F21" s="6">
-        <v>3095.5414012738856</v>
+        <v>3263.2696390658175</v>
       </c>
       <c r="G21" s="6">
-        <v>1550.8662420382168</v>
+        <v>1634.8980891719746</v>
       </c>
       <c r="H21" s="6">
         <v>60</v>
@@ -2721,7 +2721,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L21" s="6">
-        <v>9.8338273187131513</v>
+        <v>9.8338273187131477</v>
       </c>
       <c r="M21" s="6">
         <v>119.20529801324503</v>
@@ -2733,24 +2733,24 @@
         <v>11</v>
       </c>
       <c r="P21" s="6">
-        <v>2.9876564346371177</v>
+        <v>2.6348653096505714</v>
       </c>
       <c r="Q21" s="6">
-        <v>32.864220781008292</v>
+        <v>28.983518406156286</v>
       </c>
       <c r="R21" s="6">
-        <v>7.4091061578395569</v>
+        <v>8.4523177081925933</v>
       </c>
       <c r="S21" s="6">
-        <v>6.9793780006848607</v>
+        <v>7.9620832811174242</v>
       </c>
       <c r="T21" s="7">
-        <v>13.930894212943834</v>
+        <v>15.892381798637571</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5">
-        <v>2917</v>
+        <v>3075</v>
       </c>
       <c r="B22" s="6">
         <v>97.701637350966649</v>
@@ -2765,10 +2765,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F22" s="6">
-        <v>3096.602972399151</v>
+        <v>3264.3312101910828</v>
       </c>
       <c r="G22" s="6">
-        <v>1551.3980891719746</v>
+        <v>1635.4299363057326</v>
       </c>
       <c r="H22" s="6">
         <v>60</v>
@@ -2783,36 +2783,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L22" s="6">
-        <v>9.8338273187131602</v>
+        <v>9.833827318713146</v>
       </c>
       <c r="M22" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N22" s="6">
-        <v>153.1265226962625</v>
+        <v>153.12652269626247</v>
       </c>
       <c r="O22" s="6">
         <v>11</v>
       </c>
       <c r="P22" s="6">
-        <v>2.9876564346371177</v>
+        <v>2.6348653096505714</v>
       </c>
       <c r="Q22" s="6">
-        <v>32.864220781008292</v>
+        <v>28.983518406156286</v>
       </c>
       <c r="R22" s="6">
-        <v>7.4065661831539753</v>
+        <v>8.4495689869866766</v>
       </c>
       <c r="S22" s="6">
-        <v>6.9769853445310446</v>
+        <v>7.9594939857414504</v>
       </c>
       <c r="T22" s="7">
-        <v>13.926118452157773</v>
+        <v>15.887213544394113</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5">
-        <v>2918</v>
+        <v>3076</v>
       </c>
       <c r="B23" s="6">
         <v>97.701637350966649</v>
@@ -2827,10 +2827,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F23" s="6">
-        <v>3097.6645435244163</v>
+        <v>3265.3927813163482</v>
       </c>
       <c r="G23" s="6">
-        <v>1551.9299363057326</v>
+        <v>1635.9617834394905</v>
       </c>
       <c r="H23" s="6">
         <v>60</v>
@@ -2845,36 +2845,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L23" s="6">
-        <v>9.8338273187131389</v>
+        <v>9.8338273187131531</v>
       </c>
       <c r="M23" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N23" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O23" s="6">
         <v>11</v>
       </c>
       <c r="P23" s="6">
-        <v>2.9876564346371177</v>
+        <v>2.6348653096505714</v>
       </c>
       <c r="Q23" s="6">
-        <v>32.864220781008292</v>
+        <v>28.983518406156286</v>
       </c>
       <c r="R23" s="6">
-        <v>7.4040279493694809</v>
+        <v>8.4468220529857074</v>
       </c>
       <c r="S23" s="6">
-        <v>6.9745943283060505</v>
+        <v>7.9569063739125356</v>
       </c>
       <c r="T23" s="7">
-        <v>13.921345964682736</v>
+        <v>15.882048650524021</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5">
-        <v>2919</v>
+        <v>3077</v>
       </c>
       <c r="B24" s="6">
         <v>97.701637350966649</v>
@@ -2889,10 +2889,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F24" s="6">
-        <v>3098.7261146496817</v>
+        <v>3266.454352441614</v>
       </c>
       <c r="G24" s="6">
-        <v>1552.4617834394905</v>
+        <v>1636.4936305732485</v>
       </c>
       <c r="H24" s="6">
         <v>60</v>
@@ -2907,36 +2907,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L24" s="6">
-        <v>9.8338273187131566</v>
+        <v>9.8338273187131406</v>
       </c>
       <c r="M24" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N24" s="6">
-        <v>153.1265226962625</v>
+        <v>153.12652269626247</v>
       </c>
       <c r="O24" s="6">
         <v>11</v>
       </c>
       <c r="P24" s="6">
-        <v>2.9876564346371177</v>
+        <v>2.6348653096505714</v>
       </c>
       <c r="Q24" s="6">
-        <v>32.864220781008292</v>
+        <v>28.983518406156286</v>
       </c>
       <c r="R24" s="6">
-        <v>7.4014914546968642</v>
+        <v>8.4440769044472006</v>
       </c>
       <c r="S24" s="6">
-        <v>6.9722049503244445</v>
+        <v>7.9543204439892623</v>
       </c>
       <c r="T24" s="7">
-        <v>13.916576747154581</v>
+        <v>15.876887113751023</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5">
-        <v>2920</v>
+        <v>3078</v>
       </c>
       <c r="B25" s="6">
         <v>97.701637350966649</v>
@@ -2951,10 +2951,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F25" s="6">
-        <v>3099.787685774947</v>
+        <v>3267.5159235668793</v>
       </c>
       <c r="G25" s="6">
-        <v>1552.9936305732485</v>
+        <v>1637.0254777070065</v>
       </c>
       <c r="H25" s="6">
         <v>60</v>
@@ -2969,36 +2969,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L25" s="6">
-        <v>9.833827318713146</v>
+        <v>9.8338273187131477</v>
       </c>
       <c r="M25" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N25" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O25" s="6">
         <v>11</v>
       </c>
       <c r="P25" s="6">
-        <v>2.9876564346371177</v>
+        <v>2.6348653096505714</v>
       </c>
       <c r="Q25" s="6">
-        <v>32.864220781008292</v>
+        <v>28.983518406156286</v>
       </c>
       <c r="R25" s="6">
-        <v>7.398956697349365</v>
+        <v>8.441333539630941</v>
       </c>
       <c r="S25" s="6">
-        <v>6.9698172089031019</v>
+        <v>7.9517361943323452</v>
       </c>
       <c r="T25" s="7">
-        <v>13.911810796213773</v>
+        <v>15.871728930803085</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5">
-        <v>2921</v>
+        <v>3079</v>
       </c>
       <c r="B26" s="6">
         <v>97.701637350966649</v>
@@ -3013,10 +3013,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F26" s="6">
-        <v>3100.8492569002124</v>
+        <v>3268.5774946921447</v>
       </c>
       <c r="G26" s="6">
-        <v>1553.5254777070063</v>
+        <v>1637.5573248407645</v>
       </c>
       <c r="H26" s="6">
         <v>60</v>
@@ -3031,36 +3031,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L26" s="6">
-        <v>9.8338273187131442</v>
+        <v>9.8338273187131477</v>
       </c>
       <c r="M26" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N26" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O26" s="6">
         <v>11</v>
       </c>
       <c r="P26" s="6">
-        <v>2.9876564346371177</v>
+        <v>2.6348653096505714</v>
       </c>
       <c r="Q26" s="6">
-        <v>32.864220781008292</v>
+        <v>28.983518406156286</v>
       </c>
       <c r="R26" s="6">
-        <v>7.3964236755426729</v>
+        <v>8.4385919567989713</v>
       </c>
       <c r="S26" s="6">
-        <v>6.9674311023611972</v>
+        <v>7.9491536233046318</v>
       </c>
       <c r="T26" s="7">
-        <v>13.907048108505384</v>
+        <v>15.866574098412437</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5">
-        <v>2922</v>
+        <v>3080</v>
       </c>
       <c r="B27" s="6">
         <v>97.701637350966649</v>
@@ -3075,10 +3075,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F27" s="6">
-        <v>3101.9108280254777</v>
+        <v>3269.63906581741</v>
       </c>
       <c r="G27" s="6">
-        <v>1554.0573248407643</v>
+        <v>1638.0891719745225</v>
       </c>
       <c r="H27" s="6">
         <v>60</v>
@@ -3093,7 +3093,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L27" s="6">
-        <v>9.8338273187131531</v>
+        <v>9.8338273187131637</v>
       </c>
       <c r="M27" s="6">
         <v>119.20529801324503</v>
@@ -3105,24 +3105,24 @@
         <v>11</v>
       </c>
       <c r="P27" s="6">
-        <v>2.9876564346371177</v>
+        <v>2.6348653096505714</v>
       </c>
       <c r="Q27" s="6">
-        <v>32.864220781008292</v>
+        <v>28.983518406156286</v>
       </c>
       <c r="R27" s="6">
-        <v>7.3938923874949163</v>
+        <v>8.4358521542155955</v>
       </c>
       <c r="S27" s="6">
-        <v>6.965046629020212</v>
+        <v>7.9465727292710904</v>
       </c>
       <c r="T27" s="7">
-        <v>13.902288680679066</v>
+        <v>15.861422613315549</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5">
-        <v>2923</v>
+        <v>3081</v>
       </c>
       <c r="B28" s="6">
         <v>97.701637350966649</v>
@@ -3137,10 +3137,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F28" s="6">
-        <v>3102.9723991507431</v>
+        <v>3270.7006369426754</v>
       </c>
       <c r="G28" s="6">
-        <v>1554.5891719745223</v>
+        <v>1638.6210191082803</v>
       </c>
       <c r="H28" s="6">
         <v>60</v>
@@ -3155,7 +3155,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L28" s="6">
-        <v>9.8338273187131513</v>
+        <v>9.8338273187131531</v>
       </c>
       <c r="M28" s="6">
         <v>119.20529801324503</v>
@@ -3167,24 +3167,24 @@
         <v>11</v>
       </c>
       <c r="P28" s="6">
-        <v>2.9876564346371177</v>
+        <v>2.6348653096505714</v>
       </c>
       <c r="Q28" s="6">
-        <v>32.864220781008292</v>
+        <v>28.983518406156286</v>
       </c>
       <c r="R28" s="6">
-        <v>7.3913628314266653</v>
+        <v>8.4331141301473664</v>
       </c>
       <c r="S28" s="6">
-        <v>6.9626637872039199</v>
+        <v>7.9439935105988191</v>
       </c>
       <c r="T28" s="7">
-        <v>13.897532509389062</v>
+        <v>15.856274472253132</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5">
-        <v>2924</v>
+        <v>3082</v>
       </c>
       <c r="B29" s="6">
         <v>97.701637350966649</v>
@@ -3199,10 +3199,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F29" s="6">
-        <v>3104.0339702760089</v>
+        <v>3271.7622080679407</v>
       </c>
       <c r="G29" s="6">
-        <v>1555.1210191082805</v>
+        <v>1639.1528662420383</v>
       </c>
       <c r="H29" s="6">
         <v>60</v>
@@ -3217,36 +3217,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L29" s="6">
-        <v>9.8338273187131566</v>
+        <v>9.8338273187131424</v>
       </c>
       <c r="M29" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N29" s="6">
-        <v>153.1265226962625</v>
+        <v>153.12652269626247</v>
       </c>
       <c r="O29" s="6">
         <v>11</v>
       </c>
       <c r="P29" s="6">
-        <v>2.9876564346371177</v>
+        <v>2.6348653096505714</v>
       </c>
       <c r="Q29" s="6">
-        <v>32.864220781008292</v>
+        <v>28.983518406156286</v>
       </c>
       <c r="R29" s="6">
-        <v>7.3888350055609253</v>
+        <v>8.4303778828630875</v>
       </c>
       <c r="S29" s="6">
-        <v>6.9602825752383914</v>
+        <v>7.9414159656570273</v>
       </c>
       <c r="T29" s="7">
-        <v>13.892779591294193</v>
+        <v>15.851129671970115</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5">
-        <v>3235</v>
+        <v>3083</v>
       </c>
       <c r="B30" s="6">
         <v>97.701637350966649</v>
@@ -3261,10 +3261,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F30" s="6">
-        <v>3434.1825902335459</v>
+        <v>3272.8237791932061</v>
       </c>
       <c r="G30" s="6">
-        <v>1720.5254777070065</v>
+        <v>1639.6847133757963</v>
       </c>
       <c r="H30" s="6">
         <v>60</v>
@@ -3279,36 +3279,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L30" s="6">
-        <v>9.833827318713146</v>
+        <v>9.8338273187131495</v>
       </c>
       <c r="M30" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N30" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O30" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P30" s="6">
-        <v>2.8661017029108669</v>
+        <v>2.6348653096505714</v>
       </c>
       <c r="Q30" s="6">
-        <v>28.66101702910867</v>
+        <v>28.983518406156286</v>
       </c>
       <c r="R30" s="6">
-        <v>8.5274277868677277</v>
+        <v>8.4276434106338094</v>
       </c>
       <c r="S30" s="6">
-        <v>8.0328369752293973</v>
+        <v>7.9388400928170482</v>
       </c>
       <c r="T30" s="7">
-        <v>16.033606736984826</v>
+        <v>15.845988209215664</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5">
-        <v>3236</v>
+        <v>3084</v>
       </c>
       <c r="B31" s="6">
         <v>97.701637350966649</v>
@@ -3323,10 +3323,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F31" s="6">
-        <v>3435.2441613588112</v>
+        <v>3273.8853503184714</v>
       </c>
       <c r="G31" s="6">
-        <v>1721.0573248407645</v>
+        <v>1640.2165605095543</v>
       </c>
       <c r="H31" s="6">
         <v>60</v>
@@ -3341,7 +3341,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L31" s="6">
-        <v>9.8338273187131602</v>
+        <v>9.8338273187131495</v>
       </c>
       <c r="M31" s="6">
         <v>119.20529801324503</v>
@@ -3350,27 +3350,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O31" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P31" s="6">
-        <v>2.8661017029108669</v>
+        <v>2.6348653096505714</v>
       </c>
       <c r="Q31" s="6">
-        <v>28.66101702910867</v>
+        <v>28.983518406156286</v>
       </c>
       <c r="R31" s="6">
-        <v>8.52479261140825</v>
+        <v>8.4249107117328244</v>
       </c>
       <c r="S31" s="6">
-        <v>8.0303546399465713</v>
+        <v>7.9362658904523213</v>
       </c>
       <c r="T31" s="7">
-        <v>16.028651975941258</v>
+        <v>15.840850080743156</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5">
-        <v>3237</v>
+        <v>3085</v>
       </c>
       <c r="B32" s="6">
         <v>97.701637350966649</v>
@@ -3385,10 +3385,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F32" s="6">
-        <v>3436.3057324840765</v>
+        <v>3274.9469214437368</v>
       </c>
       <c r="G32" s="6">
-        <v>1721.5891719745223</v>
+        <v>1640.748407643312</v>
       </c>
       <c r="H32" s="6">
         <v>60</v>
@@ -3403,7 +3403,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L32" s="6">
-        <v>9.8338273187131513</v>
+        <v>9.8338273187131477</v>
       </c>
       <c r="M32" s="6">
         <v>119.20529801324503</v>
@@ -3412,27 +3412,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O32" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P32" s="6">
-        <v>2.8661017029108669</v>
+        <v>2.6348653096505714</v>
       </c>
       <c r="Q32" s="6">
-        <v>28.66101702910867</v>
+        <v>28.983518406156286</v>
       </c>
       <c r="R32" s="6">
-        <v>8.5221590641078464</v>
+        <v>8.4221797844356683</v>
       </c>
       <c r="S32" s="6">
-        <v>8.0278738383895902</v>
+        <v>7.9336933569383987</v>
       </c>
       <c r="T32" s="7">
-        <v>16.02370027622673</v>
+        <v>15.835715283310179</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5">
-        <v>3238</v>
+        <v>3086</v>
       </c>
       <c r="B33" s="6">
         <v>97.701637350966649</v>
@@ -3447,10 +3447,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F33" s="6">
-        <v>3437.3673036093419</v>
+        <v>3276.0084925690021</v>
       </c>
       <c r="G33" s="6">
-        <v>1722.1210191082803</v>
+        <v>1641.28025477707</v>
       </c>
       <c r="H33" s="6">
         <v>60</v>
@@ -3465,36 +3465,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L33" s="6">
-        <v>9.8338273187131495</v>
+        <v>9.833827318713146</v>
       </c>
       <c r="M33" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N33" s="6">
-        <v>153.1265226962625</v>
+        <v>153.12652269626247</v>
       </c>
       <c r="O33" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P33" s="6">
-        <v>2.8661017029108669</v>
+        <v>2.6348653096505714</v>
       </c>
       <c r="Q33" s="6">
-        <v>28.66101702910867</v>
+        <v>28.983518406156286</v>
       </c>
       <c r="R33" s="6">
-        <v>8.5195271434580295</v>
+        <v>8.4194506270201028</v>
       </c>
       <c r="S33" s="6">
-        <v>8.0253945691374646</v>
+        <v>7.9311224906529363</v>
       </c>
       <c r="T33" s="7">
-        <v>16.018751635004918</v>
+        <v>15.830583813678517</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5">
-        <v>3239</v>
+        <v>3087</v>
       </c>
       <c r="B34" s="6">
         <v>97.701637350966649</v>
@@ -3509,10 +3509,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F34" s="6">
-        <v>3438.4288747346072</v>
+        <v>3277.0700636942679</v>
       </c>
       <c r="G34" s="6">
-        <v>1722.6528662420383</v>
+        <v>1641.8121019108282</v>
       </c>
       <c r="H34" s="6">
         <v>60</v>
@@ -3527,7 +3527,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L34" s="6">
-        <v>9.8338273187131566</v>
+        <v>9.8338273187131602</v>
       </c>
       <c r="M34" s="6">
         <v>119.20529801324503</v>
@@ -3536,27 +3536,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O34" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P34" s="6">
-        <v>2.8661017029108669</v>
+        <v>2.6348653096505714</v>
       </c>
       <c r="Q34" s="6">
-        <v>28.66101702910867</v>
+        <v>28.983518406156286</v>
       </c>
       <c r="R34" s="6">
-        <v>8.5168968479521752</v>
+        <v>8.4167232377661279</v>
       </c>
       <c r="S34" s="6">
-        <v>8.0229168307709493</v>
+        <v>7.9285532899756914</v>
       </c>
       <c r="T34" s="7">
-        <v>16.013806049443016</v>
+        <v>15.825455668614154</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5">
-        <v>3240</v>
+        <v>3088</v>
       </c>
       <c r="B35" s="6">
         <v>97.701637350966649</v>
@@ -3571,10 +3571,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F35" s="6">
-        <v>3439.4904458598726</v>
+        <v>3278.1316348195332</v>
       </c>
       <c r="G35" s="6">
-        <v>1723.1847133757963</v>
+        <v>1642.3439490445862</v>
       </c>
       <c r="H35" s="6">
         <v>60</v>
@@ -3589,7 +3589,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L35" s="6">
-        <v>9.8338273187131549</v>
+        <v>9.8338273187131584</v>
       </c>
       <c r="M35" s="6">
         <v>119.20529801324503</v>
@@ -3598,27 +3598,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O35" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P35" s="6">
-        <v>2.8661017029108669</v>
+        <v>2.6348653096505714</v>
       </c>
       <c r="Q35" s="6">
-        <v>28.66101702910867</v>
+        <v>28.983518406156286</v>
       </c>
       <c r="R35" s="6">
-        <v>8.5142681760855226</v>
+        <v>8.413997614955969</v>
       </c>
       <c r="S35" s="6">
-        <v>8.020440621872563</v>
+        <v>7.9259857532885238</v>
       </c>
       <c r="T35" s="7">
-        <v>16.008863516711703</v>
+        <v>15.820330844887271</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5">
-        <v>3241</v>
+        <v>3089</v>
       </c>
       <c r="B36" s="6">
         <v>97.701637350966649</v>
@@ -3633,10 +3633,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F36" s="6">
-        <v>3440.5520169851384</v>
+        <v>3279.1932059447986</v>
       </c>
       <c r="G36" s="6">
-        <v>1723.7165605095543</v>
+        <v>1642.875796178344</v>
       </c>
       <c r="H36" s="6">
         <v>60</v>
@@ -3651,7 +3651,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L36" s="6">
-        <v>9.8338273187131442</v>
+        <v>9.8338273187131406</v>
       </c>
       <c r="M36" s="6">
         <v>119.20529801324503</v>
@@ -3660,27 +3660,27 @@
         <v>153.12652269626247</v>
       </c>
       <c r="O36" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P36" s="6">
-        <v>2.8661017029108669</v>
+        <v>2.6348653096505714</v>
       </c>
       <c r="Q36" s="6">
-        <v>28.66101702910867</v>
+        <v>28.983518406156286</v>
       </c>
       <c r="R36" s="6">
-        <v>8.5116411263551672</v>
+        <v>8.4112737568740812</v>
       </c>
       <c r="S36" s="6">
-        <v>8.0179659410265671</v>
+        <v>7.9234198789753822</v>
       </c>
       <c r="T36" s="7">
-        <v>16.003924033985164</v>
+        <v>15.815209339272222</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5">
-        <v>3242</v>
+        <v>3090</v>
       </c>
       <c r="B37" s="6">
         <v>97.701637350966649</v>
@@ -3695,10 +3695,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F37" s="6">
-        <v>3441.6135881104037</v>
+        <v>3280.2547770700639</v>
       </c>
       <c r="G37" s="6">
-        <v>1724.2484076433122</v>
+        <v>1643.407643312102</v>
       </c>
       <c r="H37" s="6">
         <v>60</v>
@@ -3713,7 +3713,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L37" s="6">
-        <v>9.8338273187131602</v>
+        <v>9.8338273187131566</v>
       </c>
       <c r="M37" s="6">
         <v>119.20529801324503</v>
@@ -3722,27 +3722,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O37" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P37" s="6">
-        <v>2.8661017029108669</v>
+        <v>2.6348653096505714</v>
       </c>
       <c r="Q37" s="6">
-        <v>28.66101702910867</v>
+        <v>28.983518406156286</v>
       </c>
       <c r="R37" s="6">
-        <v>8.5090156972600557</v>
+        <v>8.4085516618071328</v>
       </c>
       <c r="S37" s="6">
-        <v>8.0154927868189709</v>
+        <v>7.9208556654223168</v>
       </c>
       <c r="T37" s="7">
-        <v>15.998987598441058</v>
+        <v>15.81009114854754</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5">
-        <v>3243</v>
+        <v>3091</v>
       </c>
       <c r="B38" s="6">
         <v>97.701637350966649</v>
@@ -3757,10 +3757,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F38" s="6">
-        <v>3442.6751592356691</v>
+        <v>3281.3163481953293</v>
       </c>
       <c r="G38" s="6">
-        <v>1724.7802547770702</v>
+        <v>1643.93949044586</v>
       </c>
       <c r="H38" s="6">
         <v>60</v>
@@ -3775,36 +3775,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L38" s="6">
-        <v>9.8338273187131495</v>
+        <v>9.833827318713146</v>
       </c>
       <c r="M38" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N38" s="6">
-        <v>153.1265226962625</v>
+        <v>153.12652269626247</v>
       </c>
       <c r="O38" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P38" s="6">
-        <v>2.8661017029108669</v>
+        <v>2.6348653096505714</v>
       </c>
       <c r="Q38" s="6">
-        <v>28.66101702910867</v>
+        <v>28.983518406156286</v>
       </c>
       <c r="R38" s="6">
-        <v>8.5063918873009854</v>
+        <v>8.4058313280440089</v>
       </c>
       <c r="S38" s="6">
-        <v>8.0130211578375281</v>
+        <v>7.9182931110174568</v>
       </c>
       <c r="T38" s="7">
-        <v>15.994054207260536</v>
+        <v>15.804976269495921</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5">
-        <v>3244</v>
+        <v>3416</v>
       </c>
       <c r="B39" s="6">
         <v>97.701637350966649</v>
@@ -3819,10 +3819,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F39" s="6">
-        <v>3443.7367303609344</v>
+        <v>3626.326963906582</v>
       </c>
       <c r="G39" s="6">
-        <v>1725.3121019108282</v>
+        <v>1816.7898089171977</v>
       </c>
       <c r="H39" s="6">
         <v>60</v>
@@ -3837,36 +3837,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L39" s="6">
-        <v>9.8338273187131566</v>
+        <v>9.833827318713146</v>
       </c>
       <c r="M39" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N39" s="6">
-        <v>153.1265226962625</v>
+        <v>153.12652269626247</v>
       </c>
       <c r="O39" s="6">
         <v>10</v>
       </c>
       <c r="P39" s="6">
-        <v>2.8661017029108669</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q39" s="6">
-        <v>28.66101702910867</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R39" s="6">
-        <v>8.5037696949806083</v>
+        <v>9.7118242035359668</v>
       </c>
       <c r="S39" s="6">
-        <v>8.0105510526717332</v>
+        <v>9.1485383997308816</v>
       </c>
       <c r="T39" s="7">
-        <v>15.98912385762821</v>
+        <v>18.260555688085589</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5">
-        <v>3245</v>
+        <v>3417</v>
       </c>
       <c r="B40" s="6">
         <v>97.701637350966649</v>
@@ -3881,10 +3881,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F40" s="6">
-        <v>3444.7983014861998</v>
+        <v>3627.3885350318474</v>
       </c>
       <c r="G40" s="6">
-        <v>1725.843949044586</v>
+        <v>1817.3216560509554</v>
       </c>
       <c r="H40" s="6">
         <v>60</v>
@@ -3899,7 +3899,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L40" s="6">
-        <v>9.8338273187131637</v>
+        <v>9.8338273187131531</v>
       </c>
       <c r="M40" s="6">
         <v>119.20529801324503</v>
@@ -3911,24 +3911,24 @@
         <v>10</v>
       </c>
       <c r="P40" s="6">
-        <v>2.8661017029108669</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q40" s="6">
-        <v>28.66101702910867</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R40" s="6">
-        <v>8.5011491188034203</v>
+        <v>9.7089819956917953</v>
       </c>
       <c r="S40" s="6">
-        <v>8.0080824699128215</v>
+        <v>9.1458610399416695</v>
       </c>
       <c r="T40" s="7">
-        <v>15.984196546732178</v>
+        <v>18.2552116565702</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5">
-        <v>3246</v>
+        <v>3418</v>
       </c>
       <c r="B41" s="6">
         <v>97.701637350966649</v>
@@ -3943,10 +3943,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F41" s="6">
-        <v>3445.8598726114651</v>
+        <v>3628.4501061571127</v>
       </c>
       <c r="G41" s="6">
-        <v>1726.375796178344</v>
+        <v>1817.8535031847134</v>
       </c>
       <c r="H41" s="6">
         <v>60</v>
@@ -3961,36 +3961,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L41" s="6">
-        <v>9.833827318713146</v>
+        <v>9.8338273187131602</v>
       </c>
       <c r="M41" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N41" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O41" s="6">
         <v>10</v>
       </c>
       <c r="P41" s="6">
-        <v>2.8661017029108669</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q41" s="6">
-        <v>28.66101702910867</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R41" s="6">
-        <v>8.4985301572757539</v>
+        <v>9.7061414509300352</v>
       </c>
       <c r="S41" s="6">
-        <v>8.0056154081537603</v>
+        <v>9.1431852467760919</v>
       </c>
       <c r="T41" s="7">
-        <v>15.979272271763994</v>
+        <v>18.249870752048089</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5">
-        <v>3247</v>
+        <v>3419</v>
       </c>
       <c r="B42" s="6">
         <v>97.701637350966649</v>
@@ -4005,10 +4005,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F42" s="6">
-        <v>3446.9214437367305</v>
+        <v>3629.5116772823781</v>
       </c>
       <c r="G42" s="6">
-        <v>1726.907643312102</v>
+        <v>1818.3853503184714</v>
       </c>
       <c r="H42" s="6">
         <v>60</v>
@@ -4023,36 +4023,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L42" s="6">
-        <v>9.8338273187131531</v>
+        <v>9.8338273187131424</v>
       </c>
       <c r="M42" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N42" s="6">
-        <v>153.1265226962625</v>
+        <v>153.12652269626247</v>
       </c>
       <c r="O42" s="6">
         <v>10</v>
       </c>
       <c r="P42" s="6">
-        <v>2.8661017029108669</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q42" s="6">
-        <v>28.66101702910867</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R42" s="6">
-        <v>8.4959128089057891</v>
+        <v>9.70330256779142</v>
       </c>
       <c r="S42" s="6">
-        <v>8.0031498659892524</v>
+        <v>9.1405110188595167</v>
       </c>
       <c r="T42" s="7">
-        <v>15.974351029918669</v>
+        <v>18.244532971775484</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5">
-        <v>3248</v>
+        <v>3420</v>
       </c>
       <c r="B43" s="6">
         <v>97.701637350966649</v>
@@ -4067,10 +4067,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F43" s="6">
-        <v>3447.9830148619958</v>
+        <v>3630.5732484076434</v>
       </c>
       <c r="G43" s="6">
-        <v>1727.43949044586</v>
+        <v>1818.9171974522294</v>
       </c>
       <c r="H43" s="6">
         <v>60</v>
@@ -4085,36 +4085,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L43" s="6">
-        <v>9.8338273187131424</v>
+        <v>9.8338273187131495</v>
       </c>
       <c r="M43" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N43" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O43" s="6">
         <v>10</v>
       </c>
       <c r="P43" s="6">
-        <v>2.8661017029108669</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q43" s="6">
-        <v>28.66101702910867</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R43" s="6">
-        <v>8.4932970722035392</v>
+        <v>9.7004653448183813</v>
       </c>
       <c r="S43" s="6">
-        <v>8.0006858420157343</v>
+        <v>9.1378383548189142</v>
       </c>
       <c r="T43" s="7">
-        <v>15.969432818394681</v>
+        <v>18.239198313011805</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5">
-        <v>3249</v>
+        <v>3421</v>
       </c>
       <c r="B44" s="6">
         <v>97.701637350966649</v>
@@ -4129,10 +4129,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F44" s="6">
-        <v>3449.0445859872611</v>
+        <v>3631.6348195329088</v>
       </c>
       <c r="G44" s="6">
-        <v>1727.9713375796177</v>
+        <v>1819.4490445859874</v>
       </c>
       <c r="H44" s="6">
         <v>60</v>
@@ -4147,7 +4147,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L44" s="6">
-        <v>9.8338273187131495</v>
+        <v>9.8338273187131477</v>
       </c>
       <c r="M44" s="6">
         <v>119.20529801324503</v>
@@ -4159,24 +4159,24 @@
         <v>10</v>
       </c>
       <c r="P44" s="6">
-        <v>2.8661017029108669</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q44" s="6">
-        <v>28.66101702910867</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R44" s="6">
-        <v>8.4906829456808541</v>
+        <v>9.6976297805550598</v>
       </c>
       <c r="S44" s="6">
-        <v>7.9982233348313656</v>
+        <v>9.1351672532828658</v>
       </c>
       <c r="T44" s="7">
-        <v>15.964517634393943</v>
+        <v>18.233866773019692</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5">
-        <v>3250</v>
+        <v>3422</v>
       </c>
       <c r="B45" s="6">
         <v>97.701637350966649</v>
@@ -4191,10 +4191,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F45" s="6">
-        <v>3450.1061571125269</v>
+        <v>3632.6963906581741</v>
       </c>
       <c r="G45" s="6">
-        <v>1728.503184713376</v>
+        <v>1819.9808917197452</v>
       </c>
       <c r="H45" s="6">
         <v>60</v>
@@ -4209,36 +4209,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L45" s="6">
-        <v>9.8338273187131389</v>
+        <v>9.8338273187131549</v>
       </c>
       <c r="M45" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N45" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O45" s="6">
         <v>10</v>
       </c>
       <c r="P45" s="6">
-        <v>2.8661017029108669</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q45" s="6">
-        <v>28.66101702910867</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R45" s="6">
-        <v>8.4880704278514152</v>
+        <v>9.6947958735473012</v>
       </c>
       <c r="S45" s="6">
-        <v>7.9957623430360316</v>
+        <v>9.1324977128815572</v>
       </c>
       <c r="T45" s="7">
-        <v>15.959605475121821</v>
+        <v>18.228538349064987</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5">
-        <v>3251</v>
+        <v>3423</v>
       </c>
       <c r="B46" s="6">
         <v>97.701637350966649</v>
@@ -4253,10 +4253,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F46" s="6">
-        <v>3451.1677282377923</v>
+        <v>3633.7579617834399</v>
       </c>
       <c r="G46" s="6">
-        <v>1729.035031847134</v>
+        <v>1820.5127388535034</v>
       </c>
       <c r="H46" s="6">
         <v>60</v>
@@ -4271,7 +4271,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L46" s="6">
-        <v>9.833827318713146</v>
+        <v>9.8338273187131442</v>
       </c>
       <c r="M46" s="6">
         <v>119.20529801324503</v>
@@ -4283,24 +4283,24 @@
         <v>10</v>
       </c>
       <c r="P46" s="6">
-        <v>2.8661017029108669</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q46" s="6">
-        <v>28.66101702910867</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R46" s="6">
-        <v>8.4854595172307281</v>
+        <v>9.6919636223426409</v>
       </c>
       <c r="S46" s="6">
-        <v>7.9933028652313451</v>
+        <v>9.129829732246769</v>
       </c>
       <c r="T46" s="7">
-        <v>15.954696337787116</v>
+        <v>18.223213038416702</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="5">
-        <v>3252</v>
+        <v>3424</v>
       </c>
       <c r="B47" s="6">
         <v>97.701637350966649</v>
@@ -4315,10 +4315,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F47" s="6">
-        <v>3452.2292993630576</v>
+        <v>3634.8195329087052</v>
       </c>
       <c r="G47" s="6">
-        <v>1729.5668789808919</v>
+        <v>1821.0445859872614</v>
       </c>
       <c r="H47" s="6">
         <v>60</v>
@@ -4333,7 +4333,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L47" s="6">
-        <v>9.8338273187131602</v>
+        <v>9.8338273187131513</v>
       </c>
       <c r="M47" s="6">
         <v>119.20529801324503</v>
@@ -4345,24 +4345,24 @@
         <v>10</v>
       </c>
       <c r="P47" s="6">
-        <v>2.8661017029108669</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q47" s="6">
-        <v>28.66101702910867</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R47" s="6">
-        <v>8.4828502123361318</v>
+        <v>9.6891330254903227</v>
       </c>
       <c r="S47" s="6">
-        <v>7.990844900020635</v>
+        <v>9.1271633100118823</v>
       </c>
       <c r="T47" s="7">
-        <v>15.949790219602065</v>
+        <v>18.217890838347071</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5">
-        <v>3642</v>
+        <v>3425</v>
       </c>
       <c r="B48" s="6">
         <v>97.701637350966649</v>
@@ -4377,10 +4377,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F48" s="6">
-        <v>3866.2420382165606</v>
+        <v>3635.8811040339706</v>
       </c>
       <c r="G48" s="6">
-        <v>1936.9872611464968</v>
+        <v>1821.5764331210194</v>
       </c>
       <c r="H48" s="6">
         <v>60</v>
@@ -4395,7 +4395,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L48" s="6">
-        <v>9.8338273187131477</v>
+        <v>9.8338273187131495</v>
       </c>
       <c r="M48" s="6">
         <v>119.20529801324503</v>
@@ -4404,27 +4404,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O48" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P48" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q48" s="6">
-        <v>24.65487838368476</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R48" s="6">
-        <v>9.9310146733035669</v>
+        <v>9.6863040815412731</v>
       </c>
       <c r="S48" s="6">
-        <v>9.3550158222519606</v>
+        <v>9.1244984448118789</v>
       </c>
       <c r="T48" s="7">
-        <v>18.67268627196</v>
+        <v>18.212571746131495</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5">
-        <v>3643</v>
+        <v>3426</v>
       </c>
       <c r="B49" s="6">
         <v>97.701637350966649</v>
@@ -4439,10 +4439,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F49" s="6">
-        <v>3867.3036093418259</v>
+        <v>3636.9426751592359</v>
       </c>
       <c r="G49" s="6">
-        <v>1937.5191082802548</v>
+        <v>1822.1082802547771</v>
       </c>
       <c r="H49" s="6">
         <v>60</v>
@@ -4457,7 +4457,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L49" s="6">
-        <v>9.8338273187131531</v>
+        <v>9.8338273187131637</v>
       </c>
       <c r="M49" s="6">
         <v>119.20529801324503</v>
@@ -4466,27 +4466,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O49" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P49" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q49" s="6">
-        <v>24.65487838368476</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R49" s="6">
-        <v>9.9282886193169357</v>
+        <v>9.6834767890481217</v>
       </c>
       <c r="S49" s="6">
-        <v>9.3524478793965518</v>
+        <v>9.1218351352833302</v>
       </c>
       <c r="T49" s="7">
-        <v>18.667560637518072</v>
+        <v>18.207255759048561</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="5">
-        <v>3644</v>
+        <v>3427</v>
       </c>
       <c r="B50" s="6">
         <v>97.701637350966649</v>
@@ -4501,10 +4501,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F50" s="6">
-        <v>3868.3651804670917</v>
+        <v>3638.0042462845013</v>
       </c>
       <c r="G50" s="6">
-        <v>1938.0509554140131</v>
+        <v>1822.6401273885351</v>
       </c>
       <c r="H50" s="6">
         <v>60</v>
@@ -4519,7 +4519,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L50" s="6">
-        <v>9.8338273187131584</v>
+        <v>9.8338273187131549</v>
       </c>
       <c r="M50" s="6">
         <v>119.20529801324503</v>
@@ -4528,27 +4528,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O50" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P50" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q50" s="6">
-        <v>24.65487838368476</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R50" s="6">
-        <v>9.925564061518001</v>
+        <v>9.680651146565177</v>
       </c>
       <c r="S50" s="6">
-        <v>9.3498813459499548</v>
+        <v>9.1191733800643959</v>
       </c>
       <c r="T50" s="7">
-        <v>18.662437816267374</v>
+        <v>18.20194287438003</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5">
-        <v>3645</v>
+        <v>3428</v>
       </c>
       <c r="B51" s="6">
         <v>97.701637350966649</v>
@@ -4563,10 +4563,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F51" s="6">
-        <v>3869.426751592357</v>
+        <v>3639.0658174097666</v>
       </c>
       <c r="G51" s="6">
-        <v>1938.5828025477708</v>
+        <v>1823.1719745222931</v>
       </c>
       <c r="H51" s="6">
         <v>60</v>
@@ -4581,7 +4581,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L51" s="6">
-        <v>9.8338273187131353</v>
+        <v>9.8338273187131371</v>
       </c>
       <c r="M51" s="6">
         <v>119.20529801324503</v>
@@ -4590,27 +4590,27 @@
         <v>153.12652269626247</v>
       </c>
       <c r="O51" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P51" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q51" s="6">
-        <v>24.65487838368476</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R51" s="6">
-        <v>9.9228409986753334</v>
+        <v>9.6778271526484421</v>
       </c>
       <c r="S51" s="6">
-        <v>9.3473162207521643</v>
+        <v>9.1165131777948325</v>
       </c>
       <c r="T51" s="7">
-        <v>18.657317805892543</v>
+        <v>18.196633089410845</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="5">
-        <v>3646</v>
+        <v>3429</v>
       </c>
       <c r="B52" s="6">
         <v>97.701637350966649</v>
@@ -4625,10 +4625,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F52" s="6">
-        <v>3870.4883227176224</v>
+        <v>3640.127388535032</v>
       </c>
       <c r="G52" s="6">
-        <v>1939.1146496815288</v>
+        <v>1823.7038216560511</v>
       </c>
       <c r="H52" s="6">
         <v>60</v>
@@ -4643,7 +4643,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L52" s="6">
-        <v>9.8338273187131424</v>
+        <v>9.8338273187131442</v>
       </c>
       <c r="M52" s="6">
         <v>119.20529801324503</v>
@@ -4652,27 +4652,27 @@
         <v>153.12652269626247</v>
       </c>
       <c r="O52" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P52" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q52" s="6">
-        <v>24.65487838368476</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R52" s="6">
-        <v>9.9201194295588575</v>
+        <v>9.6750048058556022</v>
       </c>
       <c r="S52" s="6">
-        <v>9.3447525026444431</v>
+        <v>9.1138545271159774</v>
       </c>
       <c r="T52" s="7">
-        <v>18.652200604080726</v>
+        <v>18.191326401429095</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="5">
-        <v>3647</v>
+        <v>3430</v>
       </c>
       <c r="B53" s="6">
         <v>97.701637350966649</v>
@@ -4687,10 +4687,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F53" s="6">
-        <v>3871.5498938428877</v>
+        <v>3641.1889596602973</v>
       </c>
       <c r="G53" s="6">
-        <v>1939.6464968152868</v>
+        <v>1824.2356687898089</v>
       </c>
       <c r="H53" s="6">
         <v>60</v>
@@ -4705,7 +4705,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L53" s="6">
-        <v>9.8338273187131477</v>
+        <v>9.8338273187131513</v>
       </c>
       <c r="M53" s="6">
         <v>119.20529801324503</v>
@@ -4714,27 +4714,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O53" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P53" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q53" s="6">
-        <v>24.65487838368476</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R53" s="6">
-        <v>9.9173993529398405</v>
+        <v>9.6721841047460249</v>
       </c>
       <c r="S53" s="6">
-        <v>9.3421901904693279</v>
+        <v>9.1111974266707545</v>
       </c>
       <c r="T53" s="7">
-        <v>18.64708620852161</v>
+        <v>18.186022807726058</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5">
-        <v>3648</v>
+        <v>3431</v>
       </c>
       <c r="B54" s="6">
         <v>97.701637350966649</v>
@@ -4749,10 +4749,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F54" s="6">
-        <v>3872.6114649681531</v>
+        <v>3642.2505307855627</v>
       </c>
       <c r="G54" s="6">
-        <v>1940.1783439490448</v>
+        <v>1824.7675159235669</v>
       </c>
       <c r="H54" s="6">
         <v>60</v>
@@ -4767,36 +4767,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L54" s="6">
-        <v>9.833827318713146</v>
+        <v>9.8338273187131495</v>
       </c>
       <c r="M54" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N54" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O54" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P54" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q54" s="6">
-        <v>24.65487838368476</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R54" s="6">
-        <v>9.9146807675908963</v>
+        <v>9.6693650478807527</v>
       </c>
       <c r="S54" s="6">
-        <v>9.3396292830706251</v>
+        <v>9.1085418751036684</v>
       </c>
       <c r="T54" s="7">
-        <v>18.641974616907437</v>
+        <v>18.180722305596149</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5">
-        <v>3649</v>
+        <v>3432</v>
       </c>
       <c r="B55" s="6">
         <v>97.701637350966649</v>
@@ -4811,10 +4811,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F55" s="6">
-        <v>3873.6730360934184</v>
+        <v>3643.312101910828</v>
       </c>
       <c r="G55" s="6">
-        <v>1940.7101910828026</v>
+        <v>1825.2993630573249</v>
       </c>
       <c r="H55" s="6">
         <v>60</v>
@@ -4829,7 +4829,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L55" s="6">
-        <v>9.833827318713146</v>
+        <v>9.8338273187131406</v>
       </c>
       <c r="M55" s="6">
         <v>119.20529801324503</v>
@@ -4838,27 +4838,27 @@
         <v>153.12652269626247</v>
       </c>
       <c r="O55" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P55" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q55" s="6">
-        <v>24.65487838368476</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R55" s="6">
-        <v>9.9119636722859941</v>
+        <v>9.6665476338225123</v>
       </c>
       <c r="S55" s="6">
-        <v>9.3370697792934063</v>
+        <v>9.1058878710608067</v>
       </c>
       <c r="T55" s="7">
-        <v>18.636865826932947</v>
+        <v>18.175424892336938</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5">
-        <v>3650</v>
+        <v>3433</v>
       </c>
       <c r="B56" s="6">
         <v>97.701637350966649</v>
@@ -4873,10 +4873,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F56" s="6">
-        <v>3874.7346072186838</v>
+        <v>3644.3736730360938</v>
       </c>
       <c r="G56" s="6">
-        <v>1941.2420382165606</v>
+        <v>1825.8312101910831</v>
       </c>
       <c r="H56" s="6">
         <v>60</v>
@@ -4891,36 +4891,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L56" s="6">
-        <v>9.8338273187131442</v>
+        <v>9.833827318713162</v>
       </c>
       <c r="M56" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N56" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O56" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P56" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q56" s="6">
-        <v>24.65487838368476</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R56" s="6">
-        <v>9.9092480658004369</v>
+        <v>9.6637318611357017</v>
       </c>
       <c r="S56" s="6">
-        <v>9.3345116779840094</v>
+        <v>9.1032354131898305</v>
       </c>
       <c r="T56" s="7">
-        <v>18.631759836295434</v>
+        <v>18.17013056524916</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5">
-        <v>3651</v>
+        <v>3434</v>
       </c>
       <c r="B57" s="6">
         <v>97.701637350966649</v>
@@ -4935,10 +4935,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F57" s="6">
-        <v>3875.7961783439491</v>
+        <v>3645.4352441613592</v>
       </c>
       <c r="G57" s="6">
-        <v>1941.7738853503186</v>
+        <v>1826.3630573248408</v>
       </c>
       <c r="H57" s="6">
         <v>60</v>
@@ -4953,36 +4953,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L57" s="6">
-        <v>9.8338273187131584</v>
+        <v>9.8338273187131442</v>
       </c>
       <c r="M57" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N57" s="6">
-        <v>153.1265226962625</v>
+        <v>153.12652269626247</v>
       </c>
       <c r="O57" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P57" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q57" s="6">
-        <v>24.65487838368476</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R57" s="6">
-        <v>9.9065339469108729</v>
+        <v>9.660917728386389</v>
       </c>
       <c r="S57" s="6">
-        <v>9.3319549779900406</v>
+        <v>9.1005845001399788</v>
       </c>
       <c r="T57" s="7">
-        <v>18.626656642694694</v>
+        <v>18.164839321636684</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5">
-        <v>3652</v>
+        <v>3435</v>
       </c>
       <c r="B58" s="6">
         <v>97.701637350966649</v>
@@ -4997,10 +4997,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F58" s="6">
-        <v>3876.8577494692145</v>
+        <v>3646.4968152866245</v>
       </c>
       <c r="G58" s="6">
-        <v>1942.3057324840765</v>
+        <v>1826.8949044585988</v>
       </c>
       <c r="H58" s="6">
         <v>60</v>
@@ -5015,7 +5015,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L58" s="6">
-        <v>9.8338273187131637</v>
+        <v>9.8338273187131584</v>
       </c>
       <c r="M58" s="6">
         <v>119.20529801324503</v>
@@ -5024,27 +5024,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O58" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P58" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q58" s="6">
-        <v>24.65487838368476</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R58" s="6">
-        <v>9.9038213143952873</v>
+        <v>9.6581052341423188</v>
       </c>
       <c r="S58" s="6">
-        <v>9.3293996781603621</v>
+        <v>9.0979351305620639</v>
       </c>
       <c r="T58" s="7">
-        <v>18.621556243833059</v>
+        <v>18.159551158806511</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="5">
-        <v>3653</v>
+        <v>3436</v>
       </c>
       <c r="B59" s="6">
         <v>97.701637350966649</v>
@@ -5059,10 +5059,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F59" s="6">
-        <v>3877.9193205944803</v>
+        <v>3647.5583864118898</v>
       </c>
       <c r="G59" s="6">
-        <v>1942.8375796178345</v>
+        <v>1827.4267515923568</v>
       </c>
       <c r="H59" s="6">
         <v>60</v>
@@ -5077,36 +5077,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L59" s="6">
-        <v>9.833827318713146</v>
+        <v>9.8338273187131495</v>
       </c>
       <c r="M59" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N59" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O59" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P59" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q59" s="6">
-        <v>24.65487838368476</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R59" s="6">
-        <v>9.9011101670330124</v>
+        <v>9.6552943769728934</v>
       </c>
       <c r="S59" s="6">
-        <v>9.3268457773450972</v>
+        <v>9.0952873031084653</v>
       </c>
       <c r="T59" s="7">
-        <v>18.616458637415363</v>
+        <v>18.15426607406879</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="5">
-        <v>3654</v>
+        <v>3437</v>
       </c>
       <c r="B60" s="6">
         <v>97.701637350966649</v>
@@ -5121,10 +5121,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F60" s="6">
-        <v>3878.9808917197456</v>
+        <v>3648.6199575371552</v>
       </c>
       <c r="G60" s="6">
-        <v>1943.3694267515925</v>
+        <v>1827.9585987261148</v>
       </c>
       <c r="H60" s="6">
         <v>60</v>
@@ -5139,36 +5139,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L60" s="6">
-        <v>9.833827318713146</v>
+        <v>9.8338273187131477</v>
       </c>
       <c r="M60" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N60" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O60" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P60" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q60" s="6">
-        <v>24.65487838368476</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R60" s="6">
-        <v>9.8984005036047051</v>
+        <v>9.6524851554491882</v>
       </c>
       <c r="S60" s="6">
-        <v>9.3242932743956306</v>
+        <v>9.0926410164331344</v>
       </c>
       <c r="T60" s="7">
-        <v>18.611363821148966</v>
+        <v>18.148984064736798</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5">
-        <v>3655</v>
+        <v>3438</v>
       </c>
       <c r="B61" s="6">
         <v>97.701637350966649</v>
@@ -5183,10 +5183,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F61" s="6">
-        <v>3880.042462845011</v>
+        <v>3649.6815286624205</v>
       </c>
       <c r="G61" s="6">
-        <v>1943.9012738853505</v>
+        <v>1828.4904458598726</v>
       </c>
       <c r="H61" s="6">
         <v>60</v>
@@ -5201,7 +5201,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L61" s="6">
-        <v>9.8338273187131513</v>
+        <v>9.8338273187131549</v>
       </c>
       <c r="M61" s="6">
         <v>119.20529801324503</v>
@@ -5210,27 +5210,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O61" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P61" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.5276641127069608</v>
       </c>
       <c r="Q61" s="6">
-        <v>24.65487838368476</v>
+        <v>25.27664112706961</v>
       </c>
       <c r="R61" s="6">
-        <v>9.8956923228923657</v>
+        <v>9.6496775681439395</v>
       </c>
       <c r="S61" s="6">
-        <v>9.321742168164608</v>
+        <v>9.0899962691915892</v>
       </c>
       <c r="T61" s="7">
-        <v>18.606271792743726</v>
+        <v>18.143705128126928</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5">
-        <v>3656</v>
+        <v>3847</v>
       </c>
       <c r="B62" s="6">
         <v>97.701637350966649</v>
@@ -5245,10 +5245,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F62" s="6">
-        <v>3881.1040339702763</v>
+        <v>4083.8641188959664</v>
       </c>
       <c r="G62" s="6">
-        <v>1944.4331210191085</v>
+        <v>2046.0159235668791</v>
       </c>
       <c r="H62" s="6">
         <v>60</v>
@@ -5263,7 +5263,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L62" s="6">
-        <v>9.8338273187131424</v>
+        <v>9.8338273187131389</v>
       </c>
       <c r="M62" s="6">
         <v>119.20529801324503</v>
@@ -5275,24 +5275,24 @@
         <v>9</v>
       </c>
       <c r="P62" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q62" s="6">
-        <v>24.65487838368476</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R62" s="6">
-        <v>9.892985623679321</v>
+        <v>11.306748130232355</v>
       </c>
       <c r="S62" s="6">
-        <v>9.3191924575059186</v>
+        <v>10.650956738678879</v>
       </c>
       <c r="T62" s="7">
-        <v>18.601182549912011</v>
+        <v>21.259394687981793</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5">
-        <v>3657</v>
+        <v>3848</v>
       </c>
       <c r="B63" s="6">
         <v>97.701637350966649</v>
@@ -5307,10 +5307,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F63" s="6">
-        <v>3882.1656050955417</v>
+        <v>4084.9256900212317</v>
       </c>
       <c r="G63" s="6">
-        <v>1944.9649681528663</v>
+        <v>2046.5477707006371</v>
       </c>
       <c r="H63" s="6">
         <v>60</v>
@@ -5325,36 +5325,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L63" s="6">
-        <v>9.8338273187131495</v>
+        <v>9.8338273187131442</v>
       </c>
       <c r="M63" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N63" s="6">
-        <v>153.1265226962625</v>
+        <v>153.12652269626247</v>
       </c>
       <c r="O63" s="6">
         <v>9</v>
       </c>
       <c r="P63" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q63" s="6">
-        <v>24.65487838368476</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R63" s="6">
-        <v>9.8902804047502304</v>
+        <v>11.303809786123669</v>
       </c>
       <c r="S63" s="6">
-        <v>9.3166441412747165</v>
+        <v>10.648188818528496</v>
       </c>
       <c r="T63" s="7">
-        <v>18.5960960903687</v>
+        <v>21.253869897262465</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5">
-        <v>3658</v>
+        <v>3849</v>
       </c>
       <c r="B64" s="6">
         <v>97.701637350966649</v>
@@ -5369,10 +5369,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F64" s="6">
-        <v>3883.227176220807</v>
+        <v>4085.9872611464971</v>
       </c>
       <c r="G64" s="6">
-        <v>1945.4968152866243</v>
+        <v>2047.0796178343951</v>
       </c>
       <c r="H64" s="6">
         <v>60</v>
@@ -5387,36 +5387,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L64" s="6">
-        <v>9.8338273187131549</v>
+        <v>9.8338273187131371</v>
       </c>
       <c r="M64" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N64" s="6">
-        <v>153.1265226962625</v>
+        <v>153.12652269626247</v>
       </c>
       <c r="O64" s="6">
         <v>9</v>
       </c>
       <c r="P64" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q64" s="6">
-        <v>24.65487838368476</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R64" s="6">
-        <v>9.8875766648910872</v>
+        <v>11.300872968824077</v>
       </c>
       <c r="S64" s="6">
-        <v>9.3140972183274027</v>
+        <v>10.645422336632283</v>
       </c>
       <c r="T64" s="7">
-        <v>18.591012411831144</v>
+        <v>21.248347977309937</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5">
-        <v>3659</v>
+        <v>3850</v>
       </c>
       <c r="B65" s="6">
         <v>97.701637350966649</v>
@@ -5431,10 +5431,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F65" s="6">
-        <v>3884.2887473460723</v>
+        <v>4087.0488322717624</v>
       </c>
       <c r="G65" s="6">
-        <v>1946.0286624203823</v>
+        <v>2047.6114649681531</v>
       </c>
       <c r="H65" s="6">
         <v>60</v>
@@ -5449,7 +5449,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L65" s="6">
-        <v>9.8338273187131691</v>
+        <v>9.8338273187131566</v>
       </c>
       <c r="M65" s="6">
         <v>119.20529801324503</v>
@@ -5461,24 +5461,24 @@
         <v>9</v>
       </c>
       <c r="P65" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q65" s="6">
-        <v>24.65487838368476</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R65" s="6">
-        <v>9.8848744028892028</v>
+        <v>11.297937677143862</v>
       </c>
       <c r="S65" s="6">
-        <v>9.3115516875216287</v>
+        <v>10.642657291869519</v>
       </c>
       <c r="T65" s="7">
-        <v>18.585931512019219</v>
+        <v>21.24282892588726</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5">
-        <v>3660</v>
+        <v>3851</v>
       </c>
       <c r="B66" s="6">
         <v>97.701637350966649</v>
@@ -5493,10 +5493,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F66" s="6">
-        <v>3885.3503184713377</v>
+        <v>4088.1104033970278</v>
       </c>
       <c r="G66" s="6">
-        <v>1946.5605095541403</v>
+        <v>2048.1433121019109</v>
       </c>
       <c r="H66" s="6">
         <v>60</v>
@@ -5511,7 +5511,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L66" s="6">
-        <v>9.8338273187131531</v>
+        <v>9.8338273187131549</v>
       </c>
       <c r="M66" s="6">
         <v>119.20529801324503</v>
@@ -5523,24 +5523,24 @@
         <v>9</v>
       </c>
       <c r="P66" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q66" s="6">
-        <v>24.65487838368476</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R66" s="6">
-        <v>9.8821736175332209</v>
+        <v>11.29500390989454</v>
       </c>
       <c r="S66" s="6">
-        <v>9.3090075477162948</v>
+        <v>10.639893683120656</v>
       </c>
       <c r="T66" s="7">
-        <v>18.580853388655278</v>
+        <v>21.237312740759794</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5">
-        <v>3661</v>
+        <v>3852</v>
       </c>
       <c r="B67" s="6">
         <v>97.701637350966649</v>
@@ -5555,10 +5555,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F67" s="6">
-        <v>3886.411889596603</v>
+        <v>4089.1719745222931</v>
       </c>
       <c r="G67" s="6">
-        <v>1947.092356687898</v>
+        <v>2048.6751592356691</v>
       </c>
       <c r="H67" s="6">
         <v>60</v>
@@ -5573,7 +5573,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L67" s="6">
-        <v>9.8338273187131602</v>
+        <v>9.8338273187131549</v>
       </c>
       <c r="M67" s="6">
         <v>119.20529801324503</v>
@@ -5585,24 +5585,24 @@
         <v>9</v>
       </c>
       <c r="P67" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q67" s="6">
-        <v>24.65487838368476</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R67" s="6">
-        <v>9.8794743076131102</v>
+        <v>11.292071665888857</v>
       </c>
       <c r="S67" s="6">
-        <v>9.3064647977715502</v>
+        <v>10.637131509267302</v>
       </c>
       <c r="T67" s="7">
-        <v>18.575778039464172</v>
+        <v>21.231799419695214</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5">
-        <v>3662</v>
+        <v>3853</v>
       </c>
       <c r="B68" s="6">
         <v>97.701637350966649</v>
@@ -5617,10 +5617,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F68" s="6">
-        <v>3887.4734607218684</v>
+        <v>4090.2335456475585</v>
       </c>
       <c r="G68" s="6">
-        <v>1947.624203821656</v>
+        <v>2049.2070063694268</v>
       </c>
       <c r="H68" s="6">
         <v>60</v>
@@ -5635,7 +5635,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L68" s="6">
-        <v>9.8338273187131513</v>
+        <v>9.8338273187131531</v>
       </c>
       <c r="M68" s="6">
         <v>119.20529801324503</v>
@@ -5647,24 +5647,24 @@
         <v>9</v>
       </c>
       <c r="P68" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q68" s="6">
-        <v>24.65487838368476</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R68" s="6">
-        <v>9.8767764719201523</v>
+        <v>11.289140943940792</v>
       </c>
       <c r="S68" s="6">
-        <v>9.3039234365487822</v>
+        <v>10.634370769192227</v>
       </c>
       <c r="T68" s="7">
-        <v>18.570705462173219</v>
+        <v>21.226288960463528</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5">
-        <v>3663</v>
+        <v>3854</v>
       </c>
       <c r="B69" s="6">
         <v>97.701637350966649</v>
@@ -5679,10 +5679,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F69" s="6">
-        <v>3888.5350318471342</v>
+        <v>4091.2951167728238</v>
       </c>
       <c r="G69" s="6">
-        <v>1948.1560509554142</v>
+        <v>2049.7388535031846</v>
       </c>
       <c r="H69" s="6">
         <v>60</v>
@@ -5697,7 +5697,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L69" s="6">
-        <v>9.8338273187131477</v>
+        <v>9.8338273187131655</v>
       </c>
       <c r="M69" s="6">
         <v>119.20529801324503</v>
@@ -5709,24 +5709,24 @@
         <v>9</v>
       </c>
       <c r="P69" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q69" s="6">
-        <v>24.65487838368476</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R69" s="6">
-        <v>9.8740801092469539</v>
+        <v>11.286211742865561</v>
       </c>
       <c r="S69" s="6">
-        <v>9.3013834629106285</v>
+        <v>10.631611461779357</v>
       </c>
       <c r="T69" s="7">
-        <v>18.565635654512235</v>
+        <v>21.220781360837044</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5">
-        <v>3664</v>
+        <v>3855</v>
       </c>
       <c r="B70" s="6">
         <v>97.701637350966649</v>
@@ -5741,10 +5741,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F70" s="6">
-        <v>3889.5966029723995</v>
+        <v>4092.3566878980896</v>
       </c>
       <c r="G70" s="6">
-        <v>1948.6878980891722</v>
+        <v>2050.2707006369428</v>
       </c>
       <c r="H70" s="6">
         <v>60</v>
@@ -5759,7 +5759,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L70" s="6">
-        <v>9.8338273187131549</v>
+        <v>9.8338273187131566</v>
       </c>
       <c r="M70" s="6">
         <v>119.20529801324503</v>
@@ -5771,24 +5771,24 @@
         <v>9</v>
       </c>
       <c r="P70" s="6">
-        <v>2.7394309315205287</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q70" s="6">
-        <v>24.65487838368476</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R70" s="6">
-        <v>9.8713852183874433</v>
+        <v>11.283284061479605</v>
       </c>
       <c r="S70" s="6">
-        <v>9.2988448757209703</v>
+        <v>10.628853585913786</v>
       </c>
       <c r="T70" s="7">
-        <v>18.560568614213516</v>
+        <v>21.215276618590391</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5">
-        <v>4168</v>
+        <v>3856</v>
       </c>
       <c r="B71" s="6">
         <v>97.701637350966649</v>
@@ -5803,10 +5803,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F71" s="6">
-        <v>4424.6284501061573</v>
+        <v>4093.4182590233549</v>
       </c>
       <c r="G71" s="6">
-        <v>2216.7388535031846</v>
+        <v>2050.802547770701</v>
       </c>
       <c r="H71" s="6">
         <v>60</v>
@@ -5821,7 +5821,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L71" s="6">
-        <v>9.833827318713146</v>
+        <v>9.8338273187131406</v>
       </c>
       <c r="M71" s="6">
         <v>119.20529801324503</v>
@@ -5830,27 +5830,27 @@
         <v>153.12652269626247</v>
       </c>
       <c r="O71" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P71" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q71" s="6">
-        <v>20.856170610607684</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R71" s="6">
-        <v>11.758384316653375</v>
+        <v>11.28035789860059</v>
       </c>
       <c r="S71" s="6">
-        <v>11.07639802628748</v>
+        <v>10.626097140481756</v>
       </c>
       <c r="T71" s="7">
-        <v>22.108578894785392</v>
+        <v>21.209774731500506</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5">
-        <v>4169</v>
+        <v>3857</v>
       </c>
       <c r="B72" s="6">
         <v>97.701637350966649</v>
@@ -5865,10 +5865,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F72" s="6">
-        <v>4425.6900212314231</v>
+        <v>4094.4798301486203</v>
       </c>
       <c r="G72" s="6">
-        <v>2217.2707006369428</v>
+        <v>2051.3343949044588</v>
       </c>
       <c r="H72" s="6">
         <v>60</v>
@@ -5883,7 +5883,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L72" s="6">
-        <v>9.8338273187131495</v>
+        <v>9.8338273187131477</v>
       </c>
       <c r="M72" s="6">
         <v>119.20529801324503</v>
@@ -5892,27 +5892,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O72" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P72" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q72" s="6">
-        <v>20.856170610607684</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R72" s="6">
-        <v>11.755563883859743</v>
+        <v>11.277433253047413</v>
       </c>
       <c r="S72" s="6">
-        <v>11.073741178595876</v>
+        <v>10.623342124370662</v>
       </c>
       <c r="T72" s="7">
-        <v>22.103275805580594</v>
+        <v>21.204275697346631</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5">
-        <v>4170</v>
+        <v>3858</v>
       </c>
       <c r="B73" s="6">
         <v>97.701637350966649</v>
@@ -5927,10 +5927,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F73" s="6">
-        <v>4426.751592356688</v>
+        <v>4095.5414012738856</v>
       </c>
       <c r="G73" s="6">
-        <v>2217.8025477707006</v>
+        <v>2051.8662420382166</v>
       </c>
       <c r="H73" s="6">
         <v>60</v>
@@ -5945,7 +5945,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L73" s="6">
-        <v>9.8338273187131566</v>
+        <v>9.8338273187131531</v>
       </c>
       <c r="M73" s="6">
         <v>119.20529801324503</v>
@@ -5954,27 +5954,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O73" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P73" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q73" s="6">
-        <v>20.856170610607684</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R73" s="6">
-        <v>11.752744803791671</v>
+        <v>11.274510123640196</v>
       </c>
       <c r="S73" s="6">
-        <v>11.071085605171755</v>
+        <v>10.620588536469063</v>
       </c>
       <c r="T73" s="7">
-        <v>22.097975259823862</v>
+        <v>21.19877951391031</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5">
-        <v>4171</v>
+        <v>3859</v>
       </c>
       <c r="B74" s="6">
         <v>97.701637350966649</v>
@@ -5989,10 +5989,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F74" s="6">
-        <v>4427.8131634819538</v>
+        <v>4096.6029723991505</v>
       </c>
       <c r="G74" s="6">
-        <v>2218.3343949044588</v>
+        <v>2052.3980891719743</v>
       </c>
       <c r="H74" s="6">
         <v>60</v>
@@ -6007,36 +6007,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L74" s="6">
-        <v>9.8338273187131477</v>
+        <v>9.833827318713146</v>
       </c>
       <c r="M74" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N74" s="6">
-        <v>153.1265226962625</v>
+        <v>153.12652269626247</v>
       </c>
       <c r="O74" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P74" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q74" s="6">
-        <v>20.856170610607684</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R74" s="6">
-        <v>11.749927075476208</v>
+        <v>11.271588509200278</v>
       </c>
       <c r="S74" s="6">
-        <v>11.068431305098589</v>
+        <v>10.617836375666663</v>
       </c>
       <c r="T74" s="7">
-        <v>22.092677255685803</v>
+        <v>21.193286178975374</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5">
-        <v>4172</v>
+        <v>3860</v>
       </c>
       <c r="B75" s="6">
         <v>97.701637350966649</v>
@@ -6051,10 +6051,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F75" s="6">
-        <v>4428.8747346072187</v>
+        <v>4097.6645435244163</v>
       </c>
       <c r="G75" s="6">
-        <v>2218.8662420382166</v>
+        <v>2052.9299363057326</v>
       </c>
       <c r="H75" s="6">
         <v>60</v>
@@ -6069,7 +6069,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L75" s="6">
-        <v>9.8338273187131477</v>
+        <v>9.8338273187131513</v>
       </c>
       <c r="M75" s="6">
         <v>119.20529801324503</v>
@@ -6078,27 +6078,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O75" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P75" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q75" s="6">
-        <v>20.856170610607684</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R75" s="6">
-        <v>11.74711069794134</v>
+        <v>11.268668408550226</v>
       </c>
       <c r="S75" s="6">
-        <v>11.06577827746074</v>
+        <v>10.615085640854312</v>
       </c>
       <c r="T75" s="7">
-        <v>22.087381791338807</v>
+        <v>21.18779569032797</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5">
-        <v>4173</v>
+        <v>3861</v>
       </c>
       <c r="B76" s="6">
         <v>97.701637350966649</v>
@@ -6113,10 +6113,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F76" s="6">
-        <v>4429.9363057324845</v>
+        <v>4098.7261146496821</v>
       </c>
       <c r="G76" s="6">
-        <v>2219.3980891719748</v>
+        <v>2053.4617834394908</v>
       </c>
       <c r="H76" s="6">
         <v>60</v>
@@ -6131,7 +6131,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L76" s="6">
-        <v>9.8338273187131584</v>
+        <v>9.8338273187131477</v>
       </c>
       <c r="M76" s="6">
         <v>119.20529801324503</v>
@@ -6140,27 +6140,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O76" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P76" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q76" s="6">
-        <v>20.856170610607684</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R76" s="6">
-        <v>11.744295670215976</v>
+        <v>11.265749820513824</v>
       </c>
       <c r="S76" s="6">
-        <v>11.063126521343449</v>
+        <v>10.612336330924022</v>
       </c>
       <c r="T76" s="7">
-        <v>22.082088864956983</v>
+        <v>21.182308045756532</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5">
-        <v>4174</v>
+        <v>3862</v>
       </c>
       <c r="B77" s="6">
         <v>97.701637350966649</v>
@@ -6175,10 +6175,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F77" s="6">
-        <v>4430.9978768577494</v>
+        <v>4099.787685774947</v>
       </c>
       <c r="G77" s="6">
-        <v>2219.9299363057326</v>
+        <v>2053.9936305732485</v>
       </c>
       <c r="H77" s="6">
         <v>60</v>
@@ -6193,7 +6193,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L77" s="6">
-        <v>9.8338273187131513</v>
+        <v>9.8338273187131549</v>
       </c>
       <c r="M77" s="6">
         <v>119.20529801324503</v>
@@ -6202,27 +6202,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O77" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P77" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q77" s="6">
-        <v>20.856170610607684</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R77" s="6">
-        <v>11.741481991329962</v>
+        <v>11.262832743916073</v>
       </c>
       <c r="S77" s="6">
-        <v>11.060476035832826</v>
+        <v>10.60958844476894</v>
       </c>
       <c r="T77" s="7">
-        <v>22.076798474716217</v>
+        <v>21.176823243051778</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5">
-        <v>4175</v>
+        <v>3863</v>
       </c>
       <c r="B78" s="6">
         <v>97.701637350966649</v>
@@ -6237,10 +6237,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F78" s="6">
-        <v>4432.0594479830152</v>
+        <v>4100.8492569002128</v>
       </c>
       <c r="G78" s="6">
-        <v>2220.4617834394908</v>
+        <v>2054.5254777070068</v>
       </c>
       <c r="H78" s="6">
         <v>60</v>
@@ -6255,36 +6255,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L78" s="6">
-        <v>9.8338273187131637</v>
+        <v>9.833827318713146</v>
       </c>
       <c r="M78" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N78" s="6">
-        <v>153.1265226962625</v>
+        <v>153.12652269626247</v>
       </c>
       <c r="O78" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P78" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q78" s="6">
-        <v>20.856170610607684</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R78" s="6">
-        <v>11.738669660314077</v>
+        <v>11.259917177583192</v>
       </c>
       <c r="S78" s="6">
-        <v>11.05782682001586</v>
+        <v>10.606841981283367</v>
       </c>
       <c r="T78" s="7">
-        <v>22.071510618794125</v>
+        <v>21.171341280006718</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5">
-        <v>4176</v>
+        <v>3864</v>
       </c>
       <c r="B79" s="6">
         <v>97.701637350966649</v>
@@ -6299,10 +6299,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F79" s="6">
-        <v>4433.1210191082801</v>
+        <v>4101.9108280254777</v>
       </c>
       <c r="G79" s="6">
-        <v>2220.9936305732481</v>
+        <v>2055.0573248407645</v>
       </c>
       <c r="H79" s="6">
         <v>60</v>
@@ -6317,36 +6317,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L79" s="6">
-        <v>9.8338273187131566</v>
+        <v>9.8338273187131389</v>
       </c>
       <c r="M79" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N79" s="6">
-        <v>153.1265226962625</v>
+        <v>153.12652269626247</v>
       </c>
       <c r="O79" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P79" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q79" s="6">
-        <v>20.856170610607684</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R79" s="6">
-        <v>11.735858676200015</v>
+        <v>11.257003120342619</v>
       </c>
       <c r="S79" s="6">
-        <v>11.055178872980415</v>
+        <v>10.604096939362746</v>
       </c>
       <c r="T79" s="7">
-        <v>22.066225295370092</v>
+        <v>21.165862154416654</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5">
-        <v>4177</v>
+        <v>3865</v>
       </c>
       <c r="B80" s="6">
         <v>97.701637350966649</v>
@@ -6361,10 +6361,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F80" s="6">
-        <v>4434.1825902335459</v>
+        <v>4102.9723991507435</v>
       </c>
       <c r="G80" s="6">
-        <v>2221.5254777070063</v>
+        <v>2055.5891719745223</v>
       </c>
       <c r="H80" s="6">
         <v>60</v>
@@ -6379,7 +6379,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L80" s="6">
-        <v>9.8338273187131602</v>
+        <v>9.8338273187131513</v>
       </c>
       <c r="M80" s="6">
         <v>119.20529801324503</v>
@@ -6388,27 +6388,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O80" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P80" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q80" s="6">
-        <v>20.856170610607684</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R80" s="6">
-        <v>11.733049038020415</v>
+        <v>11.254090571022994</v>
       </c>
       <c r="S80" s="6">
-        <v>11.05253219381523</v>
+        <v>10.601353317903659</v>
       </c>
       <c r="T80" s="7">
-        <v>22.06094250262521</v>
+        <v>21.160385864079167</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5">
-        <v>4178</v>
+        <v>3866</v>
       </c>
       <c r="B81" s="6">
         <v>97.701637350966649</v>
@@ -6423,10 +6423,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F81" s="6">
-        <v>4435.2441613588117</v>
+        <v>4104.0339702760084</v>
       </c>
       <c r="G81" s="6">
-        <v>2222.0573248407645</v>
+        <v>2056.1210191082801</v>
       </c>
       <c r="H81" s="6">
         <v>60</v>
@@ -6441,7 +6441,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L81" s="6">
-        <v>9.8338273187131389</v>
+        <v>9.8338273187131371</v>
       </c>
       <c r="M81" s="6">
         <v>119.20529801324503</v>
@@ -6450,27 +6450,27 @@
         <v>153.12652269626247</v>
       </c>
       <c r="O81" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P81" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q81" s="6">
-        <v>20.856170610607684</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R81" s="6">
-        <v>11.730240744808825</v>
+        <v>11.251179528454184</v>
       </c>
       <c r="S81" s="6">
-        <v>11.049886781609912</v>
+        <v>10.598611115803841</v>
       </c>
       <c r="T81" s="7">
-        <v>22.05566223874234</v>
+        <v>21.154912406794097</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5">
-        <v>4179</v>
+        <v>3867</v>
       </c>
       <c r="B82" s="6">
         <v>97.701637350966649</v>
@@ -6485,10 +6485,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F82" s="6">
-        <v>4436.3057324840765</v>
+        <v>4105.0955414012742</v>
       </c>
       <c r="G82" s="6">
-        <v>2222.5891719745223</v>
+        <v>2056.6528662420383</v>
       </c>
       <c r="H82" s="6">
         <v>60</v>
@@ -6503,36 +6503,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L82" s="6">
-        <v>9.8338273187131389</v>
+        <v>9.8338273187131549</v>
       </c>
       <c r="M82" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N82" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O82" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P82" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q82" s="6">
-        <v>20.856170610607684</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R82" s="6">
-        <v>11.727433795599728</v>
+        <v>11.248269991467255</v>
       </c>
       <c r="S82" s="6">
-        <v>11.047242635454944</v>
+        <v>10.595870331962152</v>
       </c>
       <c r="T82" s="7">
-        <v>22.050384501906077</v>
+        <v>21.149441780363581</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5">
-        <v>4180</v>
+        <v>3868</v>
       </c>
       <c r="B83" s="6">
         <v>97.701637350966649</v>
@@ -6547,10 +6547,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F83" s="6">
-        <v>4437.3673036093423</v>
+        <v>4106.1571125265391</v>
       </c>
       <c r="G83" s="6">
-        <v>2223.1210191082805</v>
+        <v>2057.184713375796</v>
       </c>
       <c r="H83" s="6">
         <v>60</v>
@@ -6565,7 +6565,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L83" s="6">
-        <v>9.8338273187131495</v>
+        <v>9.8338273187131477</v>
       </c>
       <c r="M83" s="6">
         <v>119.20529801324503</v>
@@ -6574,27 +6574,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O83" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P83" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q83" s="6">
-        <v>20.856170610607684</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R83" s="6">
-        <v>11.724628189428534</v>
+        <v>11.245361958894486</v>
       </c>
       <c r="S83" s="6">
-        <v>11.044599754441677</v>
+        <v>10.593130965278608</v>
       </c>
       <c r="T83" s="7">
-        <v>22.045109290302747</v>
+        <v>21.14397398259203</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5">
-        <v>4181</v>
+        <v>3869</v>
       </c>
       <c r="B84" s="6">
         <v>97.701637350966649</v>
@@ -6609,10 +6609,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F84" s="6">
-        <v>4438.4288747346072</v>
+        <v>4107.2186836518049</v>
       </c>
       <c r="G84" s="6">
-        <v>2223.6528662420383</v>
+        <v>2057.7165605095543</v>
       </c>
       <c r="H84" s="6">
         <v>60</v>
@@ -6627,7 +6627,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L84" s="6">
-        <v>9.8338273187131566</v>
+        <v>9.8338273187131531</v>
       </c>
       <c r="M84" s="6">
         <v>119.20529801324503</v>
@@ -6636,27 +6636,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O84" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P84" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q84" s="6">
-        <v>20.856170610607684</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R84" s="6">
-        <v>11.721823925331563</v>
+        <v>11.242455429569365</v>
       </c>
       <c r="S84" s="6">
-        <v>11.041958137662332</v>
+        <v>10.590393014654342</v>
       </c>
       <c r="T84" s="7">
-        <v>22.039836602120428</v>
+        <v>21.138509011286111</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5">
-        <v>4182</v>
+        <v>3870</v>
       </c>
       <c r="B85" s="6">
         <v>97.701637350966649</v>
@@ -6671,10 +6671,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F85" s="6">
-        <v>4439.490445859873</v>
+        <v>4108.2802547770707</v>
       </c>
       <c r="G85" s="6">
-        <v>2224.1847133757965</v>
+        <v>2058.2484076433125</v>
       </c>
       <c r="H85" s="6">
         <v>60</v>
@@ -6689,36 +6689,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L85" s="6">
-        <v>9.8338273187131549</v>
+        <v>9.8338273187131442</v>
       </c>
       <c r="M85" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N85" s="6">
-        <v>153.1265226962625</v>
+        <v>153.12652269626247</v>
       </c>
       <c r="O85" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P85" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q85" s="6">
-        <v>20.856170610607684</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R85" s="6">
-        <v>11.71902100234607</v>
+        <v>11.239550402326582</v>
       </c>
       <c r="S85" s="6">
-        <v>11.039317784209999</v>
+        <v>10.58765647899164</v>
       </c>
       <c r="T85" s="7">
-        <v>22.034566435548896</v>
+        <v>21.133046864254769</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5">
-        <v>4183</v>
+        <v>3871</v>
       </c>
       <c r="B86" s="6">
         <v>97.701637350966649</v>
@@ -6733,10 +6733,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F86" s="6">
-        <v>4440.5520169851379</v>
+        <v>4109.3418259023356</v>
       </c>
       <c r="G86" s="6">
-        <v>2224.7165605095543</v>
+        <v>2058.7802547770702</v>
       </c>
       <c r="H86" s="6">
         <v>60</v>
@@ -6751,7 +6751,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L86" s="6">
-        <v>9.8338273187131477</v>
+        <v>9.8338273187131584</v>
       </c>
       <c r="M86" s="6">
         <v>119.20529801324503</v>
@@ -6760,27 +6760,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O86" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P86" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q86" s="6">
-        <v>20.856170610607684</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R86" s="6">
-        <v>11.716219419510224</v>
+        <v>11.236646876002034</v>
       </c>
       <c r="S86" s="6">
-        <v>11.036678693178631</v>
+        <v>10.584921357193915</v>
       </c>
       <c r="T86" s="7">
-        <v>22.029298788779702</v>
+        <v>21.127587539309211</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5">
-        <v>4184</v>
+        <v>3872</v>
       </c>
       <c r="B87" s="6">
         <v>97.701637350966649</v>
@@ -6795,10 +6795,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F87" s="6">
-        <v>4441.6135881104037</v>
+        <v>4110.4033970276014</v>
       </c>
       <c r="G87" s="6">
-        <v>2225.2484076433125</v>
+        <v>2059.3121019108285</v>
       </c>
       <c r="H87" s="6">
         <v>60</v>
@@ -6813,7 +6813,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L87" s="6">
-        <v>9.8338273187131513</v>
+        <v>9.8338273187131637</v>
       </c>
       <c r="M87" s="6">
         <v>119.20529801324503</v>
@@ -6822,27 +6822,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O87" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P87" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q87" s="6">
-        <v>20.856170610607684</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R87" s="6">
-        <v>11.713419175863113</v>
+        <v>11.233744849432819</v>
       </c>
       <c r="S87" s="6">
-        <v>11.034040863663053</v>
+        <v>10.582187648165712</v>
       </c>
       <c r="T87" s="7">
-        <v>22.02403366000609</v>
+        <v>21.1221310342629</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5">
-        <v>4185</v>
+        <v>3873</v>
       </c>
       <c r="B88" s="6">
         <v>97.701637350966649</v>
@@ -6857,10 +6857,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F88" s="6">
-        <v>4442.6751592356686</v>
+        <v>4111.4649681528663</v>
       </c>
       <c r="G88" s="6">
-        <v>2225.7802547770698</v>
+        <v>2059.8439490445862</v>
       </c>
       <c r="H88" s="6">
         <v>60</v>
@@ -6875,7 +6875,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L88" s="6">
-        <v>9.8338273187131389</v>
+        <v>9.8338273187131424</v>
       </c>
       <c r="M88" s="6">
         <v>119.20529801324503</v>
@@ -6884,27 +6884,27 @@
         <v>153.12652269626247</v>
       </c>
       <c r="O88" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P88" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.4159509928804437</v>
       </c>
       <c r="Q88" s="6">
-        <v>20.856170610607684</v>
+        <v>21.743558935923993</v>
       </c>
       <c r="R88" s="6">
-        <v>11.710620270444748</v>
+        <v>11.230844321457235</v>
       </c>
       <c r="S88" s="6">
-        <v>11.031404294758952</v>
+        <v>10.579455350812717</v>
       </c>
       <c r="T88" s="7">
-        <v>22.018771047423058</v>
+        <v>21.116677346931564</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5">
-        <v>4186</v>
+        <v>4403</v>
       </c>
       <c r="B89" s="6">
         <v>97.701637350966649</v>
@@ -6919,10 +6919,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F89" s="6">
-        <v>4443.7367303609344</v>
+        <v>4674.0976645435248</v>
       </c>
       <c r="G89" s="6">
-        <v>2226.312101910828</v>
+        <v>2341.7229299363062</v>
       </c>
       <c r="H89" s="6">
         <v>60</v>
@@ -6937,36 +6937,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L89" s="6">
-        <v>9.8338273187131442</v>
+        <v>9.8338273187131531</v>
       </c>
       <c r="M89" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N89" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O89" s="6">
         <v>8</v>
       </c>
       <c r="P89" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q89" s="6">
-        <v>20.856170610607684</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R89" s="6">
-        <v>11.707822702296051</v>
+        <v>13.386067628312119</v>
       </c>
       <c r="S89" s="6">
-        <v>11.028768985562879</v>
+        <v>12.609675705870014</v>
       </c>
       <c r="T89" s="7">
-        <v>22.013510949227307</v>
+        <v>25.169013384970089</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5">
-        <v>4187</v>
+        <v>4404</v>
       </c>
       <c r="B90" s="6">
         <v>97.701637350966649</v>
@@ -6981,10 +6981,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F90" s="6">
-        <v>4444.7983014862002</v>
+        <v>4675.1592356687897</v>
       </c>
       <c r="G90" s="6">
-        <v>2226.8439490445862</v>
+        <v>2342.2547770700635</v>
       </c>
       <c r="H90" s="6">
         <v>60</v>
@@ -6999,36 +6999,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L90" s="6">
-        <v>9.8338273187131406</v>
+        <v>9.8338273187131655</v>
       </c>
       <c r="M90" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N90" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O90" s="6">
         <v>8</v>
       </c>
       <c r="P90" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q90" s="6">
-        <v>20.856170610607684</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R90" s="6">
-        <v>11.705026470458865</v>
+        <v>13.383028103419223</v>
       </c>
       <c r="S90" s="6">
-        <v>11.02613493517225</v>
+        <v>12.606812473420907</v>
       </c>
       <c r="T90" s="7">
-        <v>22.008253363617264</v>
+        <v>25.163298350141535</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5">
-        <v>4188</v>
+        <v>4405</v>
       </c>
       <c r="B91" s="6">
         <v>97.701637350966649</v>
@@ -7043,10 +7043,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F91" s="6">
-        <v>4445.8598726114651</v>
+        <v>4676.2208067940555</v>
       </c>
       <c r="G91" s="6">
-        <v>2227.375796178344</v>
+        <v>2342.7866242038217</v>
       </c>
       <c r="H91" s="6">
         <v>60</v>
@@ -7061,7 +7061,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L91" s="6">
-        <v>9.8338273187131353</v>
+        <v>9.833827318713146</v>
       </c>
       <c r="M91" s="6">
         <v>119.20529801324503</v>
@@ -7073,24 +7073,24 @@
         <v>8</v>
       </c>
       <c r="P91" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q91" s="6">
-        <v>20.856170610607684</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R91" s="6">
-        <v>11.702231573975949</v>
+        <v>13.37998995856033</v>
       </c>
       <c r="S91" s="6">
-        <v>11.023502142685341</v>
+        <v>12.603950540963831</v>
       </c>
       <c r="T91" s="7">
-        <v>22.002998288793098</v>
+        <v>25.157585910107446</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5">
-        <v>4189</v>
+        <v>4406</v>
       </c>
       <c r="B92" s="6">
         <v>97.701637350966649</v>
@@ -7105,10 +7105,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F92" s="6">
-        <v>4446.9214437367309</v>
+        <v>4677.2823779193204</v>
       </c>
       <c r="G92" s="6">
-        <v>2227.9076433121022</v>
+        <v>2343.3184713375795</v>
       </c>
       <c r="H92" s="6">
         <v>60</v>
@@ -7123,36 +7123,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L92" s="6">
-        <v>9.833827318713146</v>
+        <v>9.8338273187131584</v>
       </c>
       <c r="M92" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N92" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O92" s="6">
         <v>8</v>
       </c>
       <c r="P92" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q92" s="6">
-        <v>20.856170610607684</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R92" s="6">
-        <v>11.699438011890969</v>
+        <v>13.376953192795792</v>
       </c>
       <c r="S92" s="6">
-        <v>11.020870607201292</v>
+        <v>12.601089907613636</v>
       </c>
       <c r="T92" s="7">
-        <v>21.997745722956669</v>
+        <v>25.151876063101067</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5">
-        <v>4190</v>
+        <v>4407</v>
       </c>
       <c r="B93" s="6">
         <v>97.701637350966649</v>
@@ -7167,10 +7167,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F93" s="6">
-        <v>4447.9830148619958</v>
+        <v>4678.3439490445862</v>
       </c>
       <c r="G93" s="6">
-        <v>2228.43949044586</v>
+        <v>2343.8503184713377</v>
       </c>
       <c r="H93" s="6">
         <v>60</v>
@@ -7185,36 +7185,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L93" s="6">
-        <v>9.8338273187131531</v>
+        <v>9.8338273187131442</v>
       </c>
       <c r="M93" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N93" s="6">
-        <v>153.1265226962625</v>
+        <v>153.12652269626247</v>
       </c>
       <c r="O93" s="6">
         <v>8</v>
       </c>
       <c r="P93" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q93" s="6">
-        <v>20.856170610607684</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R93" s="6">
-        <v>11.696645783248512</v>
+        <v>13.373917805186807</v>
       </c>
       <c r="S93" s="6">
-        <v>11.018240327820099</v>
+        <v>12.598230572485972</v>
       </c>
       <c r="T93" s="7">
-        <v>21.992495664311576</v>
+        <v>25.146168807357231</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5">
-        <v>4191</v>
+        <v>4408</v>
       </c>
       <c r="B94" s="6">
         <v>97.701637350966649</v>
@@ -7229,10 +7229,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F94" s="6">
-        <v>4449.0445859872616</v>
+        <v>4679.405520169852</v>
       </c>
       <c r="G94" s="6">
-        <v>2228.9713375796182</v>
+        <v>2344.3821656050959</v>
       </c>
       <c r="H94" s="6">
         <v>60</v>
@@ -7247,7 +7247,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L94" s="6">
-        <v>9.8338273187131566</v>
+        <v>9.8338273187131531</v>
       </c>
       <c r="M94" s="6">
         <v>119.20529801324503</v>
@@ -7259,24 +7259,24 @@
         <v>8</v>
       </c>
       <c r="P94" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q94" s="6">
-        <v>20.856170610607684</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R94" s="6">
-        <v>11.693854887094075</v>
+        <v>13.370883794795429</v>
       </c>
       <c r="S94" s="6">
-        <v>11.015611303642618</v>
+        <v>12.595372534697294</v>
       </c>
       <c r="T94" s="7">
-        <v>21.98724811106311</v>
+        <v>25.140464141112364</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5">
-        <v>4192</v>
+        <v>4409</v>
       </c>
       <c r="B95" s="6">
         <v>97.701637350966649</v>
@@ -7291,10 +7291,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F95" s="6">
-        <v>4450.1061571125265</v>
+        <v>4680.4670912951169</v>
       </c>
       <c r="G95" s="6">
-        <v>2229.503184713376</v>
+        <v>2344.9140127388537</v>
       </c>
       <c r="H95" s="6">
         <v>60</v>
@@ -7309,7 +7309,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L95" s="6">
-        <v>9.8338273187131566</v>
+        <v>9.8338273187131477</v>
       </c>
       <c r="M95" s="6">
         <v>119.20529801324503</v>
@@ -7321,24 +7321,24 @@
         <v>8</v>
       </c>
       <c r="P95" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q95" s="6">
-        <v>20.856170610607684</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R95" s="6">
-        <v>11.691065322474062</v>
+        <v>13.367851160684568</v>
       </c>
       <c r="S95" s="6">
-        <v>11.012983533770566</v>
+        <v>12.592515793364862</v>
       </c>
       <c r="T95" s="7">
-        <v>21.982003061418293</v>
+        <v>25.134762062604512</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5">
-        <v>4193</v>
+        <v>4410</v>
       </c>
       <c r="B96" s="6">
         <v>97.701637350966649</v>
@@ -7353,10 +7353,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F96" s="6">
-        <v>4451.1677282377923</v>
+        <v>4681.5286624203827</v>
       </c>
       <c r="G96" s="6">
-        <v>2230.0350318471337</v>
+        <v>2345.4458598726119</v>
       </c>
       <c r="H96" s="6">
         <v>60</v>
@@ -7371,7 +7371,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L96" s="6">
-        <v>9.8338273187131406</v>
+        <v>9.833827318713146</v>
       </c>
       <c r="M96" s="6">
         <v>119.20529801324503</v>
@@ -7383,24 +7383,24 @@
         <v>8</v>
       </c>
       <c r="P96" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q96" s="6">
-        <v>20.856170610607684</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R96" s="6">
-        <v>11.688277088435791</v>
+        <v>13.364819901917972</v>
       </c>
       <c r="S96" s="6">
-        <v>11.010357017306513</v>
+        <v>12.589660347606728</v>
       </c>
       <c r="T96" s="7">
-        <v>21.976760513585855</v>
+        <v>25.129062570073309</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5">
-        <v>4194</v>
+        <v>4411</v>
       </c>
       <c r="B97" s="6">
         <v>97.701637350966649</v>
@@ -7415,10 +7415,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F97" s="6">
-        <v>4452.2292993630572</v>
+        <v>4682.5902335456476</v>
       </c>
       <c r="G97" s="6">
-        <v>2230.5668789808915</v>
+        <v>2345.9777070063697</v>
       </c>
       <c r="H97" s="6">
         <v>60</v>
@@ -7433,7 +7433,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L97" s="6">
-        <v>9.8338273187131477</v>
+        <v>9.8338273187131584</v>
       </c>
       <c r="M97" s="6">
         <v>119.20529801324503</v>
@@ -7445,24 +7445,24 @@
         <v>8</v>
       </c>
       <c r="P97" s="6">
-        <v>2.6070213263259605</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q97" s="6">
-        <v>20.856170610607684</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R97" s="6">
-        <v>11.685490184027485</v>
+        <v>13.361790017560249</v>
       </c>
       <c r="S97" s="6">
-        <v>11.007731753353891</v>
+        <v>12.586806196541753</v>
       </c>
       <c r="T97" s="7">
-        <v>21.971520465776226</v>
+        <v>25.123365661759983</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5">
-        <v>4870</v>
+        <v>4412</v>
       </c>
       <c r="B98" s="6">
         <v>97.701637350966649</v>
@@ -7477,10 +7477,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F98" s="6">
-        <v>5169.8513800424635</v>
+        <v>4683.6518046709134</v>
       </c>
       <c r="G98" s="6">
-        <v>2590.0955414012742</v>
+        <v>2346.5095541401274</v>
       </c>
       <c r="H98" s="6">
         <v>60</v>
@@ -7495,7 +7495,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L98" s="6">
-        <v>9.8338273187131549</v>
+        <v>9.833827318713162</v>
       </c>
       <c r="M98" s="6">
         <v>119.20529801324503</v>
@@ -7504,27 +7504,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O98" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P98" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q98" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R98" s="6">
-        <v>14.221714835908704</v>
+        <v>13.358761506676849</v>
       </c>
       <c r="S98" s="6">
-        <v>13.396855375425998</v>
+        <v>12.583953339289591</v>
       </c>
       <c r="T98" s="7">
-        <v>26.740230290271452</v>
+        <v>25.117671335907371</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5">
-        <v>4871</v>
+        <v>4413</v>
       </c>
       <c r="B99" s="6">
         <v>97.701637350966649</v>
@@ -7539,10 +7539,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F99" s="6">
-        <v>5170.9129511677284</v>
+        <v>4684.7133757961783</v>
       </c>
       <c r="G99" s="6">
-        <v>2590.627388535032</v>
+        <v>2347.0414012738852</v>
       </c>
       <c r="H99" s="6">
         <v>60</v>
@@ -7557,36 +7557,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L99" s="6">
-        <v>9.8338273187131442</v>
+        <v>9.8338273187131495</v>
       </c>
       <c r="M99" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N99" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O99" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P99" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q99" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R99" s="6">
-        <v>14.21879516544352</v>
+        <v>13.355734368334071</v>
       </c>
       <c r="S99" s="6">
-        <v>13.394105045847796</v>
+        <v>12.581101774970694</v>
       </c>
       <c r="T99" s="7">
-        <v>26.734740610474642</v>
+        <v>25.111979590759873</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5">
-        <v>4872</v>
+        <v>4414</v>
       </c>
       <c r="B100" s="6">
         <v>97.701637350966649</v>
@@ -7601,10 +7601,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F100" s="6">
-        <v>5171.9745222929942</v>
+        <v>4685.7749469214441</v>
       </c>
       <c r="G100" s="6">
-        <v>2591.1592356687902</v>
+        <v>2347.5732484076434</v>
       </c>
       <c r="H100" s="6">
         <v>60</v>
@@ -7619,36 +7619,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L100" s="6">
-        <v>9.8338273187131424</v>
+        <v>9.8338273187131477</v>
       </c>
       <c r="M100" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N100" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O100" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P100" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q100" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R100" s="6">
-        <v>14.215876693529431</v>
+        <v>13.352708601599062</v>
       </c>
       <c r="S100" s="6">
-        <v>13.391355845304725</v>
+        <v>12.578251502706316</v>
       </c>
       <c r="T100" s="7">
-        <v>26.729253184240964</v>
+        <v>25.106290424563504</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5">
-        <v>4873</v>
+        <v>4415</v>
       </c>
       <c r="B101" s="6">
         <v>97.701637350966649</v>
@@ -7663,10 +7663,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F101" s="6">
-        <v>5173.036093418259</v>
+        <v>4686.836518046709</v>
       </c>
       <c r="G101" s="6">
-        <v>2591.691082802548</v>
+        <v>2348.1050955414012</v>
       </c>
       <c r="H101" s="6">
         <v>60</v>
@@ -7681,36 +7681,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L101" s="6">
-        <v>9.8338273187131424</v>
+        <v>9.8338273187131477</v>
       </c>
       <c r="M101" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N101" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O101" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P101" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q101" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R101" s="6">
-        <v>14.212959419428564</v>
+        <v>13.349684205539809</v>
       </c>
       <c r="S101" s="6">
-        <v>13.388607773101707</v>
+        <v>12.5754025216185</v>
       </c>
       <c r="T101" s="7">
-        <v>26.723768010183047</v>
+        <v>25.100603835565867</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5">
-        <v>4874</v>
+        <v>4416</v>
       </c>
       <c r="B102" s="6">
         <v>97.701637350966649</v>
@@ -7725,10 +7725,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F102" s="6">
-        <v>5174.0976645435248</v>
+        <v>4687.8980891719748</v>
       </c>
       <c r="G102" s="6">
-        <v>2592.2229299363062</v>
+        <v>2348.6369426751594</v>
       </c>
       <c r="H102" s="6">
         <v>60</v>
@@ -7752,27 +7752,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O102" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P102" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q102" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R102" s="6">
-        <v>14.210043342403653</v>
+        <v>13.346661179225148</v>
       </c>
       <c r="S102" s="6">
-        <v>13.385860828544239</v>
+        <v>12.572554830830091</v>
       </c>
       <c r="T102" s="7">
-        <v>26.718285086914641</v>
+        <v>25.094919822016148</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5">
-        <v>4875</v>
+        <v>4417</v>
       </c>
       <c r="B103" s="6">
         <v>97.701637350966649</v>
@@ -7787,10 +7787,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F103" s="6">
-        <v>5175.1592356687897</v>
+        <v>4688.9596602972406</v>
       </c>
       <c r="G103" s="6">
-        <v>2592.7547770700635</v>
+        <v>2349.1687898089176</v>
       </c>
       <c r="H103" s="6">
         <v>60</v>
@@ -7805,7 +7805,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L103" s="6">
-        <v>9.8338273187131406</v>
+        <v>9.8338273187131371</v>
       </c>
       <c r="M103" s="6">
         <v>119.20529801324503</v>
@@ -7814,27 +7814,27 @@
         <v>153.12652269626247</v>
       </c>
       <c r="O103" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P103" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q103" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R103" s="6">
-        <v>14.20712846171803</v>
+        <v>13.343639521724759</v>
       </c>
       <c r="S103" s="6">
-        <v>13.383115010938383</v>
+        <v>12.56970842946472</v>
       </c>
       <c r="T103" s="7">
-        <v>26.712804413050666</v>
+        <v>25.08923838216511</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5">
-        <v>4876</v>
+        <v>4418</v>
       </c>
       <c r="B104" s="6">
         <v>97.701637350966649</v>
@@ -7849,10 +7849,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F104" s="6">
-        <v>5176.2208067940555</v>
+        <v>4690.0212314225055</v>
       </c>
       <c r="G104" s="6">
-        <v>2593.2866242038217</v>
+        <v>2349.7006369426754</v>
       </c>
       <c r="H104" s="6">
         <v>60</v>
@@ -7867,7 +7867,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L104" s="6">
-        <v>9.8338273187131602</v>
+        <v>9.833827318713162</v>
       </c>
       <c r="M104" s="6">
         <v>119.20529801324503</v>
@@ -7876,27 +7876,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O104" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P104" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q104" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R104" s="6">
-        <v>14.20421477663564</v>
+        <v>13.340619232109157</v>
       </c>
       <c r="S104" s="6">
-        <v>13.380370319590776</v>
+        <v>12.566863316646824</v>
       </c>
       <c r="T104" s="7">
-        <v>26.707325987207138</v>
+        <v>25.083559514265119</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5">
-        <v>4877</v>
+        <v>4419</v>
       </c>
       <c r="B105" s="6">
         <v>97.701637350966649</v>
@@ -7911,10 +7911,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F105" s="6">
-        <v>5177.2823779193204</v>
+        <v>4691.0828025477713</v>
       </c>
       <c r="G105" s="6">
-        <v>2593.8184713375795</v>
+        <v>2350.2324840764336</v>
       </c>
       <c r="H105" s="6">
         <v>60</v>
@@ -7929,7 +7929,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L105" s="6">
-        <v>9.8338273187131602</v>
+        <v>9.8338273187131549</v>
       </c>
       <c r="M105" s="6">
         <v>119.20529801324503</v>
@@ -7938,27 +7938,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O105" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P105" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q105" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R105" s="6">
-        <v>14.201302286421036</v>
+        <v>13.337600309449709</v>
       </c>
       <c r="S105" s="6">
-        <v>13.377626753808615</v>
+        <v>12.564019491501623</v>
       </c>
       <c r="T105" s="7">
-        <v>26.701849808001231</v>
+        <v>25.077883216570104</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5">
-        <v>4878</v>
+        <v>4420</v>
       </c>
       <c r="B106" s="6">
         <v>97.701637350966649</v>
@@ -7973,10 +7973,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F106" s="6">
-        <v>5178.3439490445862</v>
+        <v>4692.1443736730362</v>
       </c>
       <c r="G106" s="6">
-        <v>2594.3503184713377</v>
+        <v>2350.7643312101909</v>
       </c>
       <c r="H106" s="6">
         <v>60</v>
@@ -7991,7 +7991,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L106" s="6">
-        <v>9.8338273187131477</v>
+        <v>9.8338273187131531</v>
       </c>
       <c r="M106" s="6">
         <v>119.20529801324503</v>
@@ -8000,27 +8000,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O106" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P106" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q106" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R106" s="6">
-        <v>14.198390990339359</v>
+        <v>13.33458275281861</v>
       </c>
       <c r="S106" s="6">
-        <v>13.374884312899677</v>
+        <v>12.56117695315513</v>
       </c>
       <c r="T106" s="7">
-        <v>26.696375874051249</v>
+        <v>25.072209487335595</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5">
-        <v>4879</v>
+        <v>4421</v>
       </c>
       <c r="B107" s="6">
         <v>97.701637350966649</v>
@@ -8035,10 +8035,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F107" s="6">
-        <v>5179.405520169852</v>
+        <v>4693.205944798302</v>
       </c>
       <c r="G107" s="6">
-        <v>2594.8821656050959</v>
+        <v>2351.2961783439491</v>
       </c>
       <c r="H107" s="6">
         <v>60</v>
@@ -8053,36 +8053,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L107" s="6">
-        <v>9.8338273187131335</v>
+        <v>9.8338273187131584</v>
       </c>
       <c r="M107" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N107" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O107" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P107" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q107" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R107" s="6">
-        <v>14.195480887656363</v>
+        <v>13.331566561288906</v>
       </c>
       <c r="S107" s="6">
-        <v>13.372142996172292</v>
+        <v>12.558335700734149</v>
       </c>
       <c r="T107" s="7">
-        <v>26.690904183976627</v>
+        <v>25.066538324818662</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5">
-        <v>4880</v>
+        <v>4422</v>
       </c>
       <c r="B108" s="6">
         <v>97.701637350966649</v>
@@ -8097,10 +8097,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F108" s="6">
-        <v>5180.4670912951169</v>
+        <v>4694.2675159235669</v>
       </c>
       <c r="G108" s="6">
-        <v>2595.4140127388537</v>
+        <v>2351.8280254777069</v>
       </c>
       <c r="H108" s="6">
         <v>60</v>
@@ -8115,36 +8115,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L108" s="6">
-        <v>9.833827318713146</v>
+        <v>9.8338273187131513</v>
       </c>
       <c r="M108" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N108" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O108" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P108" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q108" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R108" s="6">
-        <v>14.192571977638401</v>
+        <v>13.328551733934479</v>
       </c>
       <c r="S108" s="6">
-        <v>13.369402802935374</v>
+        <v>12.555495733366277</v>
       </c>
       <c r="T108" s="7">
-        <v>26.685434736397948</v>
+        <v>25.060869727278</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5">
-        <v>4881</v>
+        <v>4423</v>
       </c>
       <c r="B109" s="6">
         <v>97.701637350966649</v>
@@ -8159,10 +8159,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F109" s="6">
-        <v>5181.5286624203827</v>
+        <v>4695.3290870488327</v>
       </c>
       <c r="G109" s="6">
-        <v>2595.9458598726119</v>
+        <v>2352.3598726114651</v>
       </c>
       <c r="H109" s="6">
         <v>60</v>
@@ -8177,36 +8177,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L109" s="6">
-        <v>9.8338273187131442</v>
+        <v>9.8338273187131495</v>
       </c>
       <c r="M109" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N109" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O109" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P109" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q109" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R109" s="6">
-        <v>14.189664259552424</v>
+        <v>13.325538269830037</v>
       </c>
       <c r="S109" s="6">
-        <v>13.366663732498385</v>
+        <v>12.552657050179896</v>
       </c>
       <c r="T109" s="7">
-        <v>26.679967529936896</v>
+        <v>25.055203692973841</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5">
-        <v>4882</v>
+        <v>4424</v>
       </c>
       <c r="B110" s="6">
         <v>97.701637350966649</v>
@@ -8221,10 +8221,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F110" s="6">
-        <v>5182.5902335456476</v>
+        <v>4696.3906581740976</v>
       </c>
       <c r="G110" s="6">
-        <v>2596.4777070063697</v>
+        <v>2352.8917197452229</v>
       </c>
       <c r="H110" s="6">
         <v>60</v>
@@ -8239,7 +8239,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L110" s="6">
-        <v>9.8338273187131442</v>
+        <v>9.8338273187131371</v>
       </c>
       <c r="M110" s="6">
         <v>119.20529801324503</v>
@@ -8248,27 +8248,27 @@
         <v>153.12652269626247</v>
       </c>
       <c r="O110" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P110" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q110" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R110" s="6">
-        <v>14.186757732665997</v>
+        <v>13.322526168051143</v>
       </c>
       <c r="S110" s="6">
-        <v>13.363925784171368</v>
+        <v>12.549819650304178</v>
       </c>
       <c r="T110" s="7">
-        <v>26.674502563216304</v>
+        <v>25.049540220168016</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5">
-        <v>4883</v>
+        <v>4425</v>
       </c>
       <c r="B111" s="6">
         <v>97.701637350966649</v>
@@ -8283,10 +8283,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F111" s="6">
-        <v>5183.6518046709134</v>
+        <v>4697.4522292993634</v>
       </c>
       <c r="G111" s="6">
-        <v>2597.0095541401274</v>
+        <v>2353.4235668789811</v>
       </c>
       <c r="H111" s="6">
         <v>60</v>
@@ -8301,7 +8301,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L111" s="6">
-        <v>9.8338273187131531</v>
+        <v>9.8338273187131549</v>
       </c>
       <c r="M111" s="6">
         <v>119.20529801324503</v>
@@ -8310,27 +8310,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O111" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P111" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q111" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R111" s="6">
-        <v>14.183852396247264</v>
+        <v>13.319515427674183</v>
       </c>
       <c r="S111" s="6">
-        <v>13.361188957264922</v>
+        <v>12.546983532869078</v>
       </c>
       <c r="T111" s="7">
-        <v>26.669039834860126</v>
+        <v>25.043879307123913</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5">
-        <v>4884</v>
+        <v>4426</v>
       </c>
       <c r="B112" s="6">
         <v>97.701637350966649</v>
@@ -8345,10 +8345,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F112" s="6">
-        <v>5184.7133757961783</v>
+        <v>4698.5138004246292</v>
       </c>
       <c r="G112" s="6">
-        <v>2597.5414012738852</v>
+        <v>2353.9554140127393</v>
       </c>
       <c r="H112" s="6">
         <v>60</v>
@@ -8363,36 +8363,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L112" s="6">
-        <v>9.8338273187131637</v>
+        <v>9.833827318713146</v>
       </c>
       <c r="M112" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N112" s="6">
-        <v>153.1265226962625</v>
+        <v>153.12652269626247</v>
       </c>
       <c r="O112" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P112" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q112" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R112" s="6">
-        <v>14.180948249564986</v>
+        <v>13.316506047776379</v>
       </c>
       <c r="S112" s="6">
-        <v>13.358453251090218</v>
+        <v>12.544148697005349</v>
       </c>
       <c r="T112" s="7">
-        <v>26.663579343493449</v>
+        <v>25.038220952106482</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5">
-        <v>4885</v>
+        <v>4427</v>
       </c>
       <c r="B113" s="6">
         <v>97.701637350966649</v>
@@ -8407,10 +8407,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F113" s="6">
-        <v>5185.7749469214441</v>
+        <v>4699.575371549894</v>
       </c>
       <c r="G113" s="6">
-        <v>2598.0732484076434</v>
+        <v>2354.4872611464971</v>
       </c>
       <c r="H113" s="6">
         <v>60</v>
@@ -8425,7 +8425,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L113" s="6">
-        <v>9.833827318713162</v>
+        <v>9.8338273187131513</v>
       </c>
       <c r="M113" s="6">
         <v>119.20529801324503</v>
@@ -8434,27 +8434,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O113" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P113" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q113" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R113" s="6">
-        <v>14.178045291888514</v>
+        <v>13.313498027435795</v>
       </c>
       <c r="S113" s="6">
-        <v>13.35571866495898</v>
+        <v>12.541315141844516</v>
       </c>
       <c r="T113" s="7">
-        <v>26.658121087742476</v>
+        <v>25.032565153382269</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5">
-        <v>4886</v>
+        <v>4428</v>
       </c>
       <c r="B114" s="6">
         <v>97.701637350966649</v>
@@ -8469,10 +8469,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F114" s="6">
-        <v>5186.836518046709</v>
+        <v>4700.6369426751598</v>
       </c>
       <c r="G114" s="6">
-        <v>2598.6050955414012</v>
+        <v>2355.0191082802553</v>
       </c>
       <c r="H114" s="6">
         <v>60</v>
@@ -8487,36 +8487,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L114" s="6">
-        <v>9.8338273187131406</v>
+        <v>9.8338273187131495</v>
       </c>
       <c r="M114" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N114" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O114" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P114" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q114" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R114" s="6">
-        <v>14.175143522487801</v>
+        <v>13.310491365731314</v>
       </c>
       <c r="S114" s="6">
-        <v>13.352985198183509</v>
+        <v>12.538482866518896</v>
       </c>
       <c r="T114" s="7">
-        <v>26.652665066234551</v>
+        <v>25.026911909219351</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5">
-        <v>4887</v>
+        <v>4429</v>
       </c>
       <c r="B115" s="6">
         <v>97.701637350966649</v>
@@ -8531,10 +8531,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F115" s="6">
-        <v>5187.8980891719748</v>
+        <v>4701.6985138004247</v>
       </c>
       <c r="G115" s="6">
-        <v>2599.1369426751594</v>
+        <v>2355.5509554140126</v>
       </c>
       <c r="H115" s="6">
         <v>60</v>
@@ -8549,36 +8549,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L115" s="6">
-        <v>9.8338273187131389</v>
+        <v>9.8338273187131566</v>
       </c>
       <c r="M115" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N115" s="6">
-        <v>153.12652269626247</v>
+        <v>153.1265226962625</v>
       </c>
       <c r="O115" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P115" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q115" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R115" s="6">
-        <v>14.172242940633396</v>
+        <v>13.307486061742663</v>
       </c>
       <c r="S115" s="6">
-        <v>13.350252850076657</v>
+        <v>12.535651870161589</v>
       </c>
       <c r="T115" s="7">
-        <v>26.647211277598114</v>
+        <v>25.021261217887403</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5">
-        <v>4888</v>
+        <v>4430</v>
       </c>
       <c r="B116" s="6">
         <v>97.701637350966649</v>
@@ -8593,10 +8593,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F116" s="6">
-        <v>5188.9596602972406</v>
+        <v>4702.7600849256905</v>
       </c>
       <c r="G116" s="6">
-        <v>2599.6687898089176</v>
+        <v>2356.0828025477708</v>
       </c>
       <c r="H116" s="6">
         <v>60</v>
@@ -8611,36 +8611,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L116" s="6">
-        <v>9.8338273187131477</v>
+        <v>9.8338273187131424</v>
       </c>
       <c r="M116" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N116" s="6">
-        <v>153.1265226962625</v>
+        <v>153.12652269626247</v>
       </c>
       <c r="O116" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P116" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q116" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R116" s="6">
-        <v>14.169343545596439</v>
+        <v>13.304482114550398</v>
       </c>
       <c r="S116" s="6">
-        <v>13.347521619951845</v>
+        <v>12.532822151906471</v>
       </c>
       <c r="T116" s="7">
-        <v>26.641759720462762</v>
+        <v>25.015613077657633</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5">
-        <v>4889</v>
+        <v>4431</v>
       </c>
       <c r="B117" s="6">
         <v>97.701637350966649</v>
@@ -8655,10 +8655,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F117" s="6">
-        <v>5190.0212314225055</v>
+        <v>4703.8216560509554</v>
       </c>
       <c r="G117" s="6">
-        <v>2600.2006369426754</v>
+        <v>2356.6146496815286</v>
       </c>
       <c r="H117" s="6">
         <v>60</v>
@@ -8673,7 +8673,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L117" s="6">
-        <v>9.8338273187131371</v>
+        <v>9.8338273187131424</v>
       </c>
       <c r="M117" s="6">
         <v>119.20529801324503</v>
@@ -8682,27 +8682,27 @@
         <v>153.12652269626247</v>
       </c>
       <c r="O117" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P117" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q117" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R117" s="6">
-        <v>14.166445336648678</v>
+        <v>13.301479523235896</v>
       </c>
       <c r="S117" s="6">
-        <v>13.344791507123054</v>
+        <v>12.529993710888215</v>
       </c>
       <c r="T117" s="7">
-        <v>26.636310393459187</v>
+        <v>25.009967486802825</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5">
-        <v>4890</v>
+        <v>4432</v>
       </c>
       <c r="B118" s="6">
         <v>97.701637350966649</v>
@@ -8717,10 +8717,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F118" s="6">
-        <v>5191.0828025477713</v>
+        <v>4704.8832271762212</v>
       </c>
       <c r="G118" s="6">
-        <v>2600.7324840764336</v>
+        <v>2357.1464968152868</v>
       </c>
       <c r="H118" s="6">
         <v>60</v>
@@ -8735,36 +8735,36 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L118" s="6">
-        <v>9.8338273187131566</v>
+        <v>9.833827318713146</v>
       </c>
       <c r="M118" s="6">
         <v>119.20529801324503</v>
       </c>
       <c r="N118" s="6">
-        <v>153.1265226962625</v>
+        <v>153.12652269626247</v>
       </c>
       <c r="O118" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P118" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q118" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R118" s="6">
-        <v>14.163548313062453</v>
+        <v>13.298478286881375</v>
       </c>
       <c r="S118" s="6">
-        <v>13.34206251090483</v>
+        <v>12.527166546242254</v>
       </c>
       <c r="T118" s="7">
-        <v>26.630863295219221</v>
+        <v>25.004324443597316</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5">
-        <v>4891</v>
+        <v>4433</v>
       </c>
       <c r="B119" s="6">
         <v>97.701637350966649</v>
@@ -8779,10 +8779,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F119" s="6">
-        <v>5192.1443736730362</v>
+        <v>4705.9447983014861</v>
       </c>
       <c r="G119" s="6">
-        <v>2601.2643312101909</v>
+        <v>2357.6783439490446</v>
       </c>
       <c r="H119" s="6">
         <v>60</v>
@@ -8797,7 +8797,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L119" s="6">
-        <v>9.8338273187131566</v>
+        <v>9.8338273187131584</v>
       </c>
       <c r="M119" s="6">
         <v>119.20529801324503</v>
@@ -8806,27 +8806,27 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O119" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P119" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q119" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R119" s="6">
-        <v>14.160652474110693</v>
+        <v>13.295478404569876</v>
       </c>
       <c r="S119" s="6">
-        <v>13.339334630612271</v>
+        <v>12.524340657104823</v>
       </c>
       <c r="T119" s="7">
-        <v>26.625418424375795</v>
+        <v>24.998683946317009</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5">
-        <v>4892</v>
+        <v>4434</v>
       </c>
       <c r="B120" s="6">
         <v>97.701637350966649</v>
@@ -8841,10 +8841,10 @@
         <v>45.591058026582672</v>
       </c>
       <c r="F120" s="6">
-        <v>5193.205944798302</v>
+        <v>4707.0063694267519</v>
       </c>
       <c r="G120" s="6">
-        <v>2601.7961783439491</v>
+        <v>2358.2101910828028</v>
       </c>
       <c r="H120" s="6">
         <v>60</v>
@@ -8859,7 +8859,7 @@
         <v>-36.142043607276911</v>
       </c>
       <c r="L120" s="6">
-        <v>9.8338273187131549</v>
+        <v>9.8338273187131495</v>
       </c>
       <c r="M120" s="6">
         <v>119.20529801324503</v>
@@ -8868,22 +8868,22 @@
         <v>153.1265226962625</v>
       </c>
       <c r="O120" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P120" s="6">
-        <v>2.4681656809402868</v>
+        <v>2.2991766973667525</v>
       </c>
       <c r="Q120" s="6">
-        <v>17.277159766582006</v>
+        <v>18.39341357893402</v>
       </c>
       <c r="R120" s="6">
-        <v>14.157757819066923</v>
+        <v>13.292479875385263</v>
       </c>
       <c r="S120" s="6">
-        <v>13.336607865561042</v>
+        <v>12.521516042612916</v>
       </c>
       <c r="T120" s="7">
-        <v>26.619975779562957</v>
+        <v>24.993045993239356</v>
       </c>
     </row>
     <row r="121">

--- a/Vibration_Matlab/弹簧参数组合.xlsx
+++ b/Vibration_Matlab/弹簧参数组合.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="60" uniqueCount="20">
   <si>
     <t>k1</t>
   </si>

--- a/Vibration_Matlab/弹簧参数组合.xlsx
+++ b/Vibration_Matlab/弹簧参数组合.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="60" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="280" uniqueCount="20">
   <si>
     <t>k1</t>
   </si>

--- a/Vibration_Matlab/弹簧参数组合.xlsx
+++ b/Vibration_Matlab/弹簧参数组合.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="280" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="300" uniqueCount="20">
   <si>
     <t>k1</t>
   </si>

--- a/Vibration_Matlab/弹簧参数组合.xlsx
+++ b/Vibration_Matlab/弹簧参数组合.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="300" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="440" uniqueCount="20">
   <si>
     <t>k1</t>
   </si>
